--- a/Documentation/rp-pico-2-pin-planner-LCCboards.xlsx
+++ b/Documentation/rp-pico-2-pin-planner-LCCboards.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Attic\Documents\Sandboxing\LCC_RPiPico_Turntable\Documentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Attic\Documents\GitHub\LCC-Pico-Node\LCC-RPi-Pico-Board\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A12F56-7BAD-41FC-98F8-1B4A554CDDA0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF014D01-3653-423F-AB03-D4368805D296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8475" yWindow="285" windowWidth="40470" windowHeight="15345" xr2:uid="{9994E188-9327-AB46-AF3F-8738237FB097}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9994E188-9327-AB46-AF3F-8738237FB097}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="607" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="157">
   <si>
     <t>gp0</t>
   </si>
@@ -2549,7 +2549,16 @@
       <c r="B51" s="40" t="s">
         <v>26</v>
       </c>
+      <c r="H51" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51" t="s">
+        <v>99</v>
+      </c>
       <c r="J51" t="s">
+        <v>99</v>
+      </c>
+      <c r="K51" t="s">
         <v>99</v>
       </c>
       <c r="M51" t="s">
@@ -2560,7 +2569,16 @@
       <c r="B52" s="41" t="s">
         <v>110</v>
       </c>
+      <c r="H52" t="s">
+        <v>100</v>
+      </c>
+      <c r="I52" t="s">
+        <v>100</v>
+      </c>
       <c r="J52" t="s">
+        <v>100</v>
+      </c>
+      <c r="K52" t="s">
         <v>100</v>
       </c>
       <c r="M52" t="s">

--- a/Documentation/rp-pico-2-pin-planner-LCCboards.xlsx
+++ b/Documentation/rp-pico-2-pin-planner-LCCboards.xlsx
@@ -8,14 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Attic\Documents\GitHub\LCC-Pico-Node\LCC-RPi-Pico-Board\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF014D01-3653-423F-AB03-D4368805D296}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803B32BD-B4E6-4E85-86F6-4679D647FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{9994E188-9327-AB46-AF3F-8738237FB097}"/>
+    <workbookView xWindow="11190" yWindow="1125" windowWidth="31845" windowHeight="19590" activeTab="3" xr2:uid="{9994E188-9327-AB46-AF3F-8738237FB097}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1 (2)" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet1 (3)" sheetId="3" r:id="rId3"/>
+    <sheet name="All" sheetId="1" r:id="rId1"/>
+    <sheet name="Nodes" sheetId="3" r:id="rId2"/>
+    <sheet name="Steppers" sheetId="2" r:id="rId3"/>
+    <sheet name="Breakouts" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -27,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="613" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="327">
   <si>
     <t>gp0</t>
   </si>
@@ -314,72 +315,12 @@
     <t>2.7 Node board</t>
   </si>
   <si>
-    <t>I/0-1:Pin1</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin2</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin3</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin4</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin5</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin6</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin9</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin10</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin1</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin2</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin3</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin4</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin5</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin6</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin7</t>
-  </si>
-  <si>
     <t>Vselect1</t>
   </si>
   <si>
     <t>Vselect2</t>
   </si>
   <si>
-    <t>I/0-2:Pin8</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin9</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin10</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin7 / I2C0 SDA</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin8 / I2C0 SCL</t>
-  </si>
-  <si>
     <t>Reset Button / header</t>
   </si>
   <si>
@@ -389,18 +330,6 @@
     <t>header pin</t>
   </si>
   <si>
-    <t>I/0-2:Pin1 : SPI1 SDI</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin2 : SPI1 CS</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin3 : SPI1 CLK</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin4 : SPI1 SDO</t>
-  </si>
-  <si>
     <t>LCC Rpi Pico Shield</t>
   </si>
   <si>
@@ -464,40 +393,695 @@
     <t>TT-Pin4 - NeoPixel data line</t>
   </si>
   <si>
-    <t>I/0-1:Pin7</t>
-  </si>
-  <si>
-    <t>I/0-1:Pin8</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin4 &amp; Blue Button</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin7 &amp; Gold Button</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin7 alternative</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin6 alternative</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin7 : Touch I2C0 SDA</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin8 : Touch I2C0 SCL</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin10 : open</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin9 : Touch INT</t>
-  </si>
-  <si>
-    <t>I/0-2:Pin9 : Display Reset</t>
-  </si>
-  <si>
     <t>TT-Pin1 - open</t>
+  </si>
+  <si>
+    <t>2.9 Stepper board</t>
+  </si>
+  <si>
+    <t>2.95 Node board</t>
+  </si>
+  <si>
+    <t>TT-Pin1</t>
+  </si>
+  <si>
+    <t>Stepper</t>
+  </si>
+  <si>
+    <t>Inputs</t>
+  </si>
+  <si>
+    <t>Outputs</t>
+  </si>
+  <si>
+    <t>2.95 Lite Node board</t>
+  </si>
+  <si>
+    <t>+3.3 V for board</t>
+  </si>
+  <si>
+    <t>selectable supply</t>
+  </si>
+  <si>
+    <t>Ground</t>
+  </si>
+  <si>
+    <t>+ Vin (3.3 or 5V)</t>
+  </si>
+  <si>
+    <t>D_SDO/RX</t>
+  </si>
+  <si>
+    <t>D_CS</t>
+  </si>
+  <si>
+    <t>D_CLK</t>
+  </si>
+  <si>
+    <t>D_SDI/TX</t>
+  </si>
+  <si>
+    <t>T_SDA</t>
+  </si>
+  <si>
+    <t>T_SCL</t>
+  </si>
+  <si>
+    <t>D_RST / T_RST</t>
+  </si>
+  <si>
+    <t>D_BL / T_RST / T_INT</t>
+  </si>
+  <si>
+    <t>Disp Pin 1</t>
+  </si>
+  <si>
+    <t>Disp Pin 2</t>
+  </si>
+  <si>
+    <t>Disp Pin 3</t>
+  </si>
+  <si>
+    <t>Disp Pin 4</t>
+  </si>
+  <si>
+    <t>Disp Pin 5</t>
+  </si>
+  <si>
+    <t>Disp Pin 6</t>
+  </si>
+  <si>
+    <t>Disp Pin 7</t>
+  </si>
+  <si>
+    <t>Disp Pin 8</t>
+  </si>
+  <si>
+    <t>Disp Pin 9</t>
+  </si>
+  <si>
+    <t>Disp Pin 10</t>
+  </si>
+  <si>
+    <t>Disp Pin 11</t>
+  </si>
+  <si>
+    <t>Disp Pin 12</t>
+  </si>
+  <si>
+    <t>Disp Pin 13</t>
+  </si>
+  <si>
+    <t>Disp Pin 14</t>
+  </si>
+  <si>
+    <t>Disp Pin 15</t>
+  </si>
+  <si>
+    <t>Disp Pin 16</t>
+  </si>
+  <si>
+    <t>Disp Pin 17</t>
+  </si>
+  <si>
+    <t>Disp Pin 18</t>
+  </si>
+  <si>
+    <t>Disp Pin 19</t>
+  </si>
+  <si>
+    <t>Disp Pin 20</t>
+  </si>
+  <si>
+    <t>Disp Pin 21</t>
+  </si>
+  <si>
+    <t>Disp Pin 22</t>
+  </si>
+  <si>
+    <t>Disp Pin 23</t>
+  </si>
+  <si>
+    <t>Disp Pin 24</t>
+  </si>
+  <si>
+    <t>Disp Pin 25</t>
+  </si>
+  <si>
+    <t>Disp Pin 26</t>
+  </si>
+  <si>
+    <t>Disp Pin 27</t>
+  </si>
+  <si>
+    <t>Disp Pin 28</t>
+  </si>
+  <si>
+    <t>Disp Pin 29</t>
+  </si>
+  <si>
+    <t>Disp Pin 30</t>
+  </si>
+  <si>
+    <t>Disp Pin 31</t>
+  </si>
+  <si>
+    <t>Disp Pin 32</t>
+  </si>
+  <si>
+    <t>Disp Pin 33</t>
+  </si>
+  <si>
+    <t>Disp Pin 34</t>
+  </si>
+  <si>
+    <t>Disp Pin 35</t>
+  </si>
+  <si>
+    <t>Disp Pin 36</t>
+  </si>
+  <si>
+    <t>Disp Pin 37</t>
+  </si>
+  <si>
+    <t>Disp Pin 38</t>
+  </si>
+  <si>
+    <t>Disp Pin 39</t>
+  </si>
+  <si>
+    <t>Disp Pin 40</t>
+  </si>
+  <si>
+    <t>+ Vin</t>
+  </si>
+  <si>
+    <t>nc</t>
+  </si>
+  <si>
+    <t>D_RST</t>
+  </si>
+  <si>
+    <t>D_BL</t>
+  </si>
+  <si>
+    <t>T_INT</t>
+  </si>
+  <si>
+    <t>T_RST</t>
+  </si>
+  <si>
+    <t>SDA</t>
+  </si>
+  <si>
+    <t>SCL</t>
+  </si>
+  <si>
+    <t>Bridge Sensor</t>
+  </si>
+  <si>
+    <t>Home Sensor</t>
+  </si>
+  <si>
+    <t>NeoPixel Data</t>
+  </si>
+  <si>
+    <t>+3.3 Vin</t>
+  </si>
+  <si>
+    <t>Ext Pwr: Pin 1</t>
+  </si>
+  <si>
+    <t>Ext Pwr: Pin 2</t>
+  </si>
+  <si>
+    <t>Ext Pwr: Pin 3</t>
+  </si>
+  <si>
+    <t>Bridge: Pin 1</t>
+  </si>
+  <si>
+    <t>Bridge: Pin 2</t>
+  </si>
+  <si>
+    <t>Bridge: Pin 3</t>
+  </si>
+  <si>
+    <t>Home: Pin 1</t>
+  </si>
+  <si>
+    <t>Home: Pin 2</t>
+  </si>
+  <si>
+    <t>Home: Pin 3</t>
+  </si>
+  <si>
+    <t>Pixel: Pin 1</t>
+  </si>
+  <si>
+    <t>Pixel: Pin 2</t>
+  </si>
+  <si>
+    <t>Pixel: Pin 3</t>
+  </si>
+  <si>
+    <t>IC2: Pin 1</t>
+  </si>
+  <si>
+    <t>IC2: Pin 2</t>
+  </si>
+  <si>
+    <t>IC2: Pin 3</t>
+  </si>
+  <si>
+    <t>IC2: Pin 4</t>
+  </si>
+  <si>
+    <t>Stepper: Pin 1</t>
+  </si>
+  <si>
+    <t>Stepper: Pin 2</t>
+  </si>
+  <si>
+    <t>Stepper: Pin 3</t>
+  </si>
+  <si>
+    <t>Stepper: Pin 4</t>
+  </si>
+  <si>
+    <t>Motor + Vin</t>
+  </si>
+  <si>
+    <t>+5 Vin</t>
+  </si>
+  <si>
+    <t>5 V</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t>1A</t>
+  </si>
+  <si>
+    <t>2A</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>RTP_DIN</t>
+  </si>
+  <si>
+    <t>RTP_SCLK</t>
+  </si>
+  <si>
+    <t>RTP_Pen Intr</t>
+  </si>
+  <si>
+    <t>RTP_CS</t>
+  </si>
+  <si>
+    <t>RTP_DOUT</t>
+  </si>
+  <si>
+    <t>AGND</t>
+  </si>
+  <si>
+    <t>VREF</t>
+  </si>
+  <si>
+    <t>SPI Display - Cap Touch</t>
+  </si>
+  <si>
+    <t>SPI Display - XPT2046 Rest Touch</t>
+  </si>
+  <si>
+    <t>Parallel Display - Cap Touch</t>
+  </si>
+  <si>
+    <t>D_PWR</t>
+  </si>
+  <si>
+    <t>D_D/C</t>
+  </si>
+  <si>
+    <t>+3.3 V</t>
+  </si>
+  <si>
+    <t>D_WR</t>
+  </si>
+  <si>
+    <t>DB0</t>
+  </si>
+  <si>
+    <t>DB1</t>
+  </si>
+  <si>
+    <t>DB2</t>
+  </si>
+  <si>
+    <t>DB3</t>
+  </si>
+  <si>
+    <t>DB4</t>
+  </si>
+  <si>
+    <t>DB5</t>
+  </si>
+  <si>
+    <t>DB6</t>
+  </si>
+  <si>
+    <t>DB7</t>
+  </si>
+  <si>
+    <t>+ 3.3 V</t>
+  </si>
+  <si>
+    <t>+ 5V</t>
+  </si>
+  <si>
+    <t>Home Sensor / D_RST</t>
+  </si>
+  <si>
+    <t>3.0 Node board</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin1</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin2</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin3</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin4</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin7 / I2C0 SDA</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin8 / I2C0 SCL</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin10 &amp; Blue Button</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin9</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin10</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin1</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin1 : SPI1 SDI</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin2</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin2 : SPI1 CS</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin8</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin3</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin3 : SPI1 CLK</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin7</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin4</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin4 : SPI1 SDO</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin7</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin7 : Touch I2C0 SDA</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin8</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin8 : Touch I2C0 SCL</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin9</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin9 : Display Reset</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin10</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin10 : open</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin4 &amp; Blue Button</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin8 &amp; Blue Button</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin7 &amp; Gold Button</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin9 &amp; Gold Button</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin10; I/O-3:Pin 1</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin2</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin7 alternative</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin3</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin5</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin5 &amp; Gold Button</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin6 alternative</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin4</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin6</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin5</t>
+  </si>
+  <si>
+    <t>I/O-1:Pin6</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin5</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin6</t>
+  </si>
+  <si>
+    <t>I/O-2:Pin9 : Touch INT</t>
+  </si>
+  <si>
+    <t>I/O-3:Pin1</t>
+  </si>
+  <si>
+    <t>Disp Pin 1-2</t>
+  </si>
+  <si>
+    <t>Disp Pin 3-4</t>
+  </si>
+  <si>
+    <t>I/O-1 Pin</t>
+  </si>
+  <si>
+    <t>GP</t>
+  </si>
+  <si>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Wire to</t>
+  </si>
+  <si>
+    <t>Pin 1</t>
+  </si>
+  <si>
+    <r>
+      <t>DISPLAY_SDI</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (SPI1 RX)</t>
+    </r>
+  </si>
+  <si>
+    <t>Display SDO</t>
+  </si>
+  <si>
+    <t>Pin 2</t>
+  </si>
+  <si>
+    <t>DISPLAY_CS</t>
+  </si>
+  <si>
+    <t>Display CS</t>
+  </si>
+  <si>
+    <t>Pin 3</t>
+  </si>
+  <si>
+    <t>DISPLAY_SCK</t>
+  </si>
+  <si>
+    <r>
+      <t>Display SCK </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> XPT2046 T_CLK</t>
+    </r>
+  </si>
+  <si>
+    <t>Pin 4</t>
+  </si>
+  <si>
+    <r>
+      <t>DISPLAY_SDO</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> (SPI1 TX)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>Display SDI </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>and</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t> XPT2046 T_DIN</t>
+    </r>
+  </si>
+  <si>
+    <t>Pin 7</t>
+  </si>
+  <si>
+    <t>TOUCH_MISO</t>
+  </si>
+  <si>
+    <r>
+      <t>XPT2046 T_DOUT </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF0A0A0A"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t>(only, not to display)</t>
+    </r>
+  </si>
+  <si>
+    <t>Pin 8</t>
+  </si>
+  <si>
+    <t>TOUCH_CS</t>
+  </si>
+  <si>
+    <t>XPT2046 T_CS</t>
+  </si>
+  <si>
+    <t>Pin 9</t>
+  </si>
+  <si>
+    <t>DISPLAY_RST</t>
+  </si>
+  <si>
+    <t>Display RST</t>
+  </si>
+  <si>
+    <t>GPIO-8</t>
+  </si>
+  <si>
+    <t>GPIO-9</t>
+  </si>
+  <si>
+    <t>GPIO-10</t>
+  </si>
+  <si>
+    <t>GPIO-11</t>
+  </si>
+  <si>
+    <t>GPIO-12</t>
+  </si>
+  <si>
+    <t>GPIO-13</t>
+  </si>
+  <si>
+    <t>GPIO-14</t>
+  </si>
+  <si>
+    <t>GPIO-15</t>
   </si>
 </sst>
 </file>
@@ -507,7 +1091,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]mmmm\ d\,\ yyyy;@"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="15">
     <font>
       <sz val="14"/>
       <color theme="1"/>
@@ -576,8 +1160,40 @@
       <family val="2"/>
       <scheme val="major"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color theme="9"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF0A0A0A"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF0070C0"/>
+      <name val="Aptos Display"/>
+      <family val="2"/>
+      <scheme val="major"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -623,6 +1239,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFDFDFC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -799,7 +1421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="47">
+  <cellXfs count="67">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -924,6 +1546,28 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -933,6 +1577,32 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1275,7 +1945,7 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M54"/>
+  <dimension ref="A1:Q54"/>
   <sheetFormatPr defaultColWidth="11.08984375" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="8" style="1" customWidth="1"/>
@@ -1283,38 +1953,38 @@
     <col min="3" max="3" width="10" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="8.7265625" style="1" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="9.26953125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="2.81640625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="20.26953125" hidden="1" customWidth="1"/>
-    <col min="8" max="9" width="20.26953125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="20.26953125" customWidth="1"/>
-    <col min="11" max="11" width="20.08984375" customWidth="1"/>
-    <col min="12" max="12" width="20.26953125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="24.26953125" customWidth="1"/>
+    <col min="6" max="6" width="2" style="1" customWidth="1"/>
+    <col min="7" max="8" width="20.26953125" style="1" customWidth="1"/>
+    <col min="9" max="9" width="20.26953125" customWidth="1"/>
+    <col min="10" max="12" width="20.08984375" customWidth="1"/>
+    <col min="13" max="13" width="20.26953125" customWidth="1"/>
+    <col min="14" max="14" width="20.26953125" style="1" customWidth="1"/>
+    <col min="15" max="16" width="24.26953125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" ht="18.75" thickBot="1">
+    <row r="1" spans="1:17" ht="18.75" thickBot="1">
       <c r="A1" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="44" t="s">
-        <v>124</v>
-      </c>
-      <c r="C1" s="44"/>
-      <c r="D1" s="44"/>
-      <c r="E1" s="45"/>
+      <c r="B1" s="54" t="s">
+        <v>100</v>
+      </c>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
+      <c r="G1" s="31"/>
       <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-    </row>
-    <row r="2" spans="1:13">
+    </row>
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="46">
+      <c r="C2" s="56">
         <v>46137</v>
       </c>
-      <c r="D2" s="46"/>
-    </row>
-    <row r="3" spans="1:13" ht="18.75" thickBot="1">
+      <c r="D2" s="56"/>
+    </row>
+    <row r="3" spans="1:17" ht="18.75" thickBot="1">
       <c r="B3" s="1">
         <v>0</v>
       </c>
@@ -1325,7 +1995,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:13" ht="18.75" thickBot="1">
+    <row r="4" spans="1:17" ht="18.75" thickBot="1">
       <c r="A4" s="1" t="s">
         <v>52</v>
       </c>
@@ -1333,51 +2003,60 @@
       <c r="C4" s="12"/>
       <c r="D4" s="12"/>
     </row>
-    <row r="5" spans="1:13" ht="18.75" thickBot="1">
+    <row r="5" spans="1:17" ht="18.75" thickBot="1">
       <c r="A5" s="1" t="s">
         <v>50</v>
       </c>
       <c r="B5" s="11"/>
       <c r="C5" s="11"/>
     </row>
-    <row r="6" spans="1:13" ht="18.75" thickBot="1">
+    <row r="6" spans="1:17" ht="18.75" thickBot="1">
       <c r="A6" s="1" t="s">
         <v>57</v>
       </c>
       <c r="B6" s="12"/>
       <c r="C6" s="12"/>
     </row>
-    <row r="7" spans="1:13" ht="18.75" thickBot="1">
+    <row r="7" spans="1:17" ht="18.75" thickBot="1">
       <c r="A7" s="1" t="s">
         <v>51</v>
       </c>
       <c r="B7" s="12"/>
       <c r="C7" s="37"/>
     </row>
-    <row r="8" spans="1:13" ht="18.75" thickBot="1">
+    <row r="8" spans="1:17" ht="18.75" thickBot="1">
       <c r="G8" s="30" t="s">
-        <v>128</v>
+        <v>102</v>
       </c>
       <c r="H8" s="30" t="s">
-        <v>126</v>
+        <v>101</v>
       </c>
       <c r="I8" s="30" t="s">
-        <v>125</v>
+        <v>94</v>
       </c>
       <c r="J8" s="30" t="s">
-        <v>94</v>
+        <v>105</v>
       </c>
       <c r="K8" s="30" t="s">
-        <v>129</v>
+        <v>123</v>
       </c>
       <c r="L8" s="30" t="s">
-        <v>127</v>
+        <v>245</v>
       </c>
       <c r="M8" s="30" t="s">
+        <v>104</v>
+      </c>
+      <c r="N8" s="30" t="s">
+        <v>103</v>
+      </c>
+      <c r="O8" s="30" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="9" spans="1:13">
+      <c r="P8" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17">
       <c r="A9" s="6">
         <v>1</v>
       </c>
@@ -1393,29 +2072,38 @@
       <c r="E9" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="G9" t="s">
-        <v>60</v>
+      <c r="G9" s="43" t="s">
+        <v>99</v>
       </c>
       <c r="H9" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="J9" s="42" t="s">
-        <v>95</v>
+        <v>99</v>
+      </c>
+      <c r="I9" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="J9" t="s">
+        <v>86</v>
       </c>
       <c r="K9" t="s">
         <v>86</v>
       </c>
       <c r="L9" t="s">
+        <v>86</v>
+      </c>
+      <c r="M9" t="s">
+        <v>60</v>
+      </c>
+      <c r="N9" t="s">
         <v>78</v>
       </c>
-      <c r="M9" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+      <c r="O9" t="s">
+        <v>118</v>
+      </c>
+      <c r="P9" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" s="7">
         <v>2</v>
       </c>
@@ -1431,29 +2119,38 @@
       <c r="E10" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G10" t="s">
-        <v>61</v>
+      <c r="G10" s="43" t="s">
+        <v>99</v>
       </c>
       <c r="H10" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="J10" s="42" t="s">
-        <v>96</v>
+        <v>99</v>
+      </c>
+      <c r="I10" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="J10" t="s">
+        <v>87</v>
       </c>
       <c r="K10" t="s">
         <v>87</v>
       </c>
       <c r="L10" t="s">
+        <v>87</v>
+      </c>
+      <c r="M10" t="s">
+        <v>61</v>
+      </c>
+      <c r="N10" t="s">
         <v>79</v>
       </c>
-      <c r="M10" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+      <c r="O10" t="s">
+        <v>119</v>
+      </c>
+      <c r="P10" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" s="7">
         <v>3</v>
       </c>
@@ -1461,12 +2158,12 @@
         <v>26</v>
       </c>
       <c r="E11" s="20"/>
+      <c r="G11"/>
       <c r="H11"/>
-      <c r="I11"/>
-      <c r="J11" s="42"/>
-      <c r="L11"/>
-    </row>
-    <row r="12" spans="1:13">
+      <c r="I11" s="42"/>
+      <c r="N11"/>
+    </row>
+    <row r="12" spans="1:17">
       <c r="A12" s="7">
         <v>4</v>
       </c>
@@ -1480,29 +2177,38 @@
         <v>44</v>
       </c>
       <c r="E12" s="20"/>
-      <c r="G12" s="39" t="s">
-        <v>62</v>
+      <c r="G12" t="s">
+        <v>106</v>
       </c>
       <c r="H12" t="s">
-        <v>130</v>
-      </c>
-      <c r="I12" t="s">
-        <v>130</v>
-      </c>
-      <c r="J12" s="42" t="s">
-        <v>97</v>
+        <v>106</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="J12" s="38" t="s">
+        <v>88</v>
       </c>
       <c r="K12" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="L12" t="s">
+      <c r="L12" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="M12" s="39" t="s">
+        <v>62</v>
+      </c>
+      <c r="N12" t="s">
         <v>80</v>
       </c>
-      <c r="M12" t="s">
+      <c r="O12" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="13" spans="1:13">
+      <c r="P12" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="13" spans="1:17">
       <c r="A13" s="7">
         <v>5</v>
       </c>
@@ -1517,28 +2223,37 @@
       </c>
       <c r="E13" s="20"/>
       <c r="G13" t="s">
-        <v>63</v>
+        <v>107</v>
       </c>
       <c r="H13" t="s">
-        <v>131</v>
-      </c>
-      <c r="I13" t="s">
-        <v>131</v>
-      </c>
-      <c r="J13" s="42" t="s">
-        <v>98</v>
+        <v>107</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="J13" s="38" t="s">
+        <v>89</v>
       </c>
       <c r="K13" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="L13" t="s">
+      <c r="L13" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="M13" t="s">
         <v>63</v>
       </c>
-      <c r="M13" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+      <c r="N13" t="s">
+        <v>63</v>
+      </c>
+      <c r="O13" t="s">
+        <v>120</v>
+      </c>
+      <c r="P13" s="38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="14" spans="1:17">
       <c r="A14" s="7">
         <v>6</v>
       </c>
@@ -1554,29 +2269,39 @@
       <c r="E14" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G14" t="s">
-        <v>64</v>
+      <c r="G14" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="H14" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="I14" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="J14" s="42" t="s">
-        <v>115</v>
+      <c r="I14" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="J14" s="38" t="s">
+        <v>90</v>
       </c>
       <c r="K14" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="L14" t="s">
+      <c r="L14" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="M14" t="s">
         <v>64</v>
       </c>
-      <c r="M14" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+      <c r="N14" t="s">
+        <v>64</v>
+      </c>
+      <c r="O14" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="P14" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q14" s="43"/>
+    </row>
+    <row r="15" spans="1:17">
       <c r="A15" s="7">
         <v>7</v>
       </c>
@@ -1592,29 +2317,39 @@
       <c r="E15" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G15" t="s">
-        <v>65</v>
+      <c r="G15" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="H15" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="I15" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="J15" s="42" t="s">
-        <v>116</v>
+      <c r="I15" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="J15" s="43" t="s">
+        <v>99</v>
       </c>
       <c r="K15" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="L15" t="s">
+        <v>99</v>
+      </c>
+      <c r="L15" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="M15" t="s">
         <v>65</v>
       </c>
-      <c r="M15" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+      <c r="N15" t="s">
+        <v>65</v>
+      </c>
+      <c r="O15" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="P15" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q15" s="43"/>
+    </row>
+    <row r="16" spans="1:17">
       <c r="A16" s="7">
         <v>8</v>
       </c>
@@ -1622,12 +2357,12 @@
         <v>26</v>
       </c>
       <c r="E16" s="20"/>
+      <c r="G16"/>
       <c r="H16"/>
-      <c r="I16"/>
-      <c r="J16" s="42"/>
-      <c r="L16"/>
-    </row>
-    <row r="17" spans="1:13">
+      <c r="I16" s="42"/>
+      <c r="N16"/>
+    </row>
+    <row r="17" spans="1:16">
       <c r="A17" s="7">
         <v>9</v>
       </c>
@@ -1642,28 +2377,37 @@
       </c>
       <c r="E17" s="20"/>
       <c r="G17" t="s">
-        <v>73</v>
+        <v>108</v>
       </c>
       <c r="H17" t="s">
-        <v>132</v>
-      </c>
-      <c r="I17" t="s">
-        <v>132</v>
-      </c>
-      <c r="J17" s="42" t="s">
-        <v>101</v>
+        <v>108</v>
+      </c>
+      <c r="I17" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="J17" t="s">
+        <v>44</v>
       </c>
       <c r="K17" t="s">
         <v>44</v>
       </c>
       <c r="L17" t="s">
+        <v>44</v>
+      </c>
+      <c r="M17" t="s">
         <v>73</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
+        <v>73</v>
+      </c>
+      <c r="O17" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="18" spans="1:13">
+      <c r="P17" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16">
       <c r="A18" s="7">
         <v>10</v>
       </c>
@@ -1678,28 +2422,37 @@
       </c>
       <c r="E18" s="20"/>
       <c r="G18" t="s">
-        <v>66</v>
+        <v>109</v>
       </c>
       <c r="H18" t="s">
-        <v>133</v>
-      </c>
-      <c r="I18" t="s">
-        <v>133</v>
-      </c>
-      <c r="J18" s="42" t="s">
-        <v>102</v>
+        <v>109</v>
+      </c>
+      <c r="I18" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="J18" t="s">
+        <v>45</v>
       </c>
       <c r="K18" t="s">
         <v>45</v>
       </c>
       <c r="L18" t="s">
+        <v>45</v>
+      </c>
+      <c r="M18" t="s">
         <v>66</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
+        <v>66</v>
+      </c>
+      <c r="O18" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="19" spans="1:13">
+      <c r="P18" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16">
       <c r="A19" s="7">
         <v>11</v>
       </c>
@@ -1715,29 +2468,38 @@
       <c r="E19" s="19" t="s">
         <v>48</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="H19" t="s">
+        <v>110</v>
+      </c>
+      <c r="I19" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="J19" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="K19" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="L19" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="M19" t="s">
         <v>67</v>
       </c>
-      <c r="H19" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="I19" t="s">
-        <v>134</v>
-      </c>
-      <c r="J19" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="K19" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="L19" t="s">
+      <c r="N19" t="s">
         <v>67</v>
       </c>
-      <c r="M19" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+      <c r="O19" t="s">
+        <v>256</v>
+      </c>
+      <c r="P19" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16">
       <c r="A20" s="7">
         <v>12</v>
       </c>
@@ -1753,29 +2515,38 @@
       <c r="E20" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="G20" t="s">
+      <c r="G20" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="H20" t="s">
+        <v>111</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="J20" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="K20" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="L20" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="M20" t="s">
         <v>68</v>
       </c>
-      <c r="H20" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="I20" t="s">
-        <v>135</v>
-      </c>
-      <c r="J20" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="K20" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="L20" t="s">
+      <c r="N20" t="s">
         <v>68</v>
       </c>
-      <c r="M20" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+      <c r="O20" t="s">
+        <v>258</v>
+      </c>
+      <c r="P20" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16">
       <c r="A21" s="7">
         <v>13</v>
       </c>
@@ -1783,12 +2554,14 @@
         <v>26</v>
       </c>
       <c r="E21" s="20"/>
-      <c r="H21" s="42"/>
+      <c r="G21" s="42"/>
+      <c r="I21" s="42"/>
       <c r="J21" s="42"/>
       <c r="K21" s="42"/>
-      <c r="L21"/>
-    </row>
-    <row r="22" spans="1:13">
+      <c r="L21" s="42"/>
+      <c r="N21"/>
+    </row>
+    <row r="22" spans="1:16">
       <c r="A22" s="7">
         <v>14</v>
       </c>
@@ -1802,29 +2575,38 @@
         <v>44</v>
       </c>
       <c r="E22" s="20"/>
-      <c r="G22" t="s">
+      <c r="G22" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="H22" t="s">
+        <v>117</v>
+      </c>
+      <c r="I22" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="J22" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="K22" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="L22" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="M22" t="s">
         <v>69</v>
       </c>
-      <c r="H22" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="I22" t="s">
-        <v>141</v>
-      </c>
-      <c r="J22" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="K22" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="L22" t="s">
+      <c r="N22" t="s">
         <v>69</v>
       </c>
-      <c r="M22" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+      <c r="O22" t="s">
+        <v>261</v>
+      </c>
+      <c r="P22" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="23" spans="1:16">
       <c r="A23" s="7">
         <v>15</v>
       </c>
@@ -1838,29 +2620,38 @@
         <v>45</v>
       </c>
       <c r="E23" s="20"/>
-      <c r="G23" t="s">
+      <c r="G23" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="H23" t="s">
+        <v>116</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="J23" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="K23" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="L23" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="M23" t="s">
         <v>70</v>
       </c>
-      <c r="H23" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="I23" t="s">
-        <v>140</v>
-      </c>
-      <c r="J23" s="42" t="s">
-        <v>106</v>
-      </c>
-      <c r="K23" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="L23" t="s">
+      <c r="N23" t="s">
         <v>70</v>
       </c>
-      <c r="M23" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+      <c r="O23" t="s">
+        <v>264</v>
+      </c>
+      <c r="P23" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="24" spans="1:16">
       <c r="A24" s="7">
         <v>16</v>
       </c>
@@ -1876,29 +2667,38 @@
       <c r="E24" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="G24" t="s">
+      <c r="G24" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="H24" t="s">
+        <v>115</v>
+      </c>
+      <c r="I24" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="J24" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="L24" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="M24" t="s">
         <v>71</v>
       </c>
-      <c r="H24" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="I24" t="s">
-        <v>139</v>
-      </c>
-      <c r="J24" s="42" t="s">
-        <v>109</v>
-      </c>
-      <c r="K24" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="L24" t="s">
+      <c r="N24" t="s">
         <v>71</v>
       </c>
-      <c r="M24" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+      <c r="O24" t="s">
+        <v>266</v>
+      </c>
+      <c r="P24" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="25" spans="1:16">
       <c r="A25" s="7">
         <v>17</v>
       </c>
@@ -1914,29 +2714,38 @@
       <c r="E25" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G25" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="H25" t="s">
+        <v>114</v>
+      </c>
+      <c r="I25" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="K25" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="L25" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="M25" t="s">
         <v>72</v>
       </c>
-      <c r="H25" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="I25" t="s">
-        <v>138</v>
-      </c>
-      <c r="J25" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="K25" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="L25" t="s">
+      <c r="N25" t="s">
         <v>72</v>
       </c>
-      <c r="M25" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+      <c r="O25" t="s">
+        <v>268</v>
+      </c>
+      <c r="P25" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="26" spans="1:16">
       <c r="A26" s="7">
         <v>18</v>
       </c>
@@ -1944,12 +2753,14 @@
         <v>26</v>
       </c>
       <c r="E26" s="20"/>
-      <c r="H26" s="42"/>
+      <c r="G26" s="42"/>
+      <c r="I26" s="42"/>
       <c r="J26" s="42"/>
       <c r="K26" s="42"/>
-      <c r="L26"/>
-    </row>
-    <row r="27" spans="1:13">
+      <c r="L26" s="42"/>
+      <c r="N26"/>
+    </row>
+    <row r="27" spans="1:16">
       <c r="A27" s="7">
         <v>19</v>
       </c>
@@ -1963,29 +2774,38 @@
         <v>44</v>
       </c>
       <c r="E27" s="20"/>
-      <c r="G27" t="s">
+      <c r="G27" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H27" t="s">
+        <v>113</v>
+      </c>
+      <c r="I27" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="L27" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="M27" t="s">
         <v>74</v>
       </c>
-      <c r="H27" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="I27" t="s">
-        <v>137</v>
-      </c>
-      <c r="J27" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="K27" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="L27" t="s">
+      <c r="N27" t="s">
         <v>74</v>
       </c>
-      <c r="M27" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="18.75" thickBot="1">
+      <c r="O27" t="s">
+        <v>270</v>
+      </c>
+      <c r="P27" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="28" spans="1:16" ht="18.75" thickBot="1">
       <c r="A28" s="8">
         <v>20</v>
       </c>
@@ -1999,29 +2819,38 @@
         <v>45</v>
       </c>
       <c r="E28" s="23"/>
-      <c r="G28" t="s">
+      <c r="G28" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="H28" t="s">
+        <v>112</v>
+      </c>
+      <c r="I28" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="L28" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="M28" t="s">
         <v>75</v>
       </c>
-      <c r="H28" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="I28" t="s">
-        <v>136</v>
-      </c>
-      <c r="J28" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="K28" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="L28" t="s">
+      <c r="N28" t="s">
         <v>75</v>
       </c>
-      <c r="M28" s="42" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" s="5" customFormat="1" ht="18.75" thickBot="1">
+      <c r="O28" s="42" t="s">
+        <v>272</v>
+      </c>
+      <c r="P28" s="42" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="29" spans="1:16" s="5" customFormat="1" ht="18.75" thickBot="1">
       <c r="A29" s="3"/>
       <c r="B29" s="4"/>
       <c r="C29" s="3"/>
@@ -2029,7 +2858,7 @@
       <c r="E29" s="3"/>
       <c r="F29" s="3"/>
     </row>
-    <row r="30" spans="1:13">
+    <row r="30" spans="1:16">
       <c r="A30" s="1">
         <v>21</v>
       </c>
@@ -2046,7 +2875,7 @@
         <v>46</v>
       </c>
       <c r="G30" t="s">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="H30" t="s">
         <v>86</v>
@@ -2054,20 +2883,29 @@
       <c r="I30" t="s">
         <v>86</v>
       </c>
-      <c r="J30" t="s">
+      <c r="J30" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="K30" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="L30" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="M30" t="s">
+        <v>76</v>
+      </c>
+      <c r="N30" t="s">
         <v>86</v>
       </c>
-      <c r="K30" s="1" t="s">
+      <c r="O30" t="s">
+        <v>86</v>
+      </c>
+      <c r="P30" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="L30" t="s">
-        <v>86</v>
-      </c>
-      <c r="M30" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+    </row>
+    <row r="31" spans="1:16">
       <c r="A31" s="1">
         <v>22</v>
       </c>
@@ -2084,7 +2922,7 @@
         <v>47</v>
       </c>
       <c r="G31" t="s">
-        <v>77</v>
+        <v>87</v>
       </c>
       <c r="H31" t="s">
         <v>87</v>
@@ -2092,20 +2930,29 @@
       <c r="I31" t="s">
         <v>87</v>
       </c>
-      <c r="J31" t="s">
+      <c r="J31" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="L31" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="M31" t="s">
+        <v>77</v>
+      </c>
+      <c r="N31" t="s">
         <v>87</v>
       </c>
-      <c r="K31" s="1" t="s">
+      <c r="O31" t="s">
+        <v>87</v>
+      </c>
+      <c r="P31" s="1" t="s">
         <v>43</v>
       </c>
-      <c r="L31" t="s">
-        <v>87</v>
-      </c>
-      <c r="M31" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+    </row>
+    <row r="32" spans="1:16">
       <c r="A32" s="1">
         <v>23</v>
       </c>
@@ -2113,11 +2960,11 @@
         <v>26</v>
       </c>
       <c r="E32" s="20"/>
+      <c r="G32"/>
       <c r="H32"/>
-      <c r="I32"/>
-      <c r="L32"/>
-    </row>
-    <row r="33" spans="1:13">
+      <c r="N32"/>
+    </row>
+    <row r="33" spans="1:16">
       <c r="A33" s="1">
         <v>24</v>
       </c>
@@ -2131,8 +2978,8 @@
         <v>44</v>
       </c>
       <c r="E33" s="20"/>
-      <c r="G33" t="s">
-        <v>78</v>
+      <c r="G33" s="38" t="s">
+        <v>88</v>
       </c>
       <c r="H33" s="38" t="s">
         <v>88</v>
@@ -2140,20 +2987,29 @@
       <c r="I33" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="J33" s="38" t="s">
+      <c r="J33" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="K33" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="L33" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="M33" t="s">
+        <v>78</v>
+      </c>
+      <c r="N33" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="K33" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="L33" s="38" t="s">
+      <c r="O33" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="M33" s="38" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13">
+      <c r="P33" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="34" spans="1:16">
       <c r="A34" s="1">
         <v>25</v>
       </c>
@@ -2167,8 +3023,8 @@
         <v>45</v>
       </c>
       <c r="E34" s="20"/>
-      <c r="G34" t="s">
-        <v>79</v>
+      <c r="G34" s="38" t="s">
+        <v>89</v>
       </c>
       <c r="H34" s="38" t="s">
         <v>89</v>
@@ -2176,20 +3032,29 @@
       <c r="I34" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="J34" s="38" t="s">
+      <c r="J34" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K34" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="L34" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="M34" t="s">
+        <v>79</v>
+      </c>
+      <c r="N34" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="K34" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="L34" s="38" t="s">
+      <c r="O34" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="M34" s="38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13">
+      <c r="P34" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="35" spans="1:16">
       <c r="A35" s="1">
         <v>26</v>
       </c>
@@ -2200,8 +3065,8 @@
         <v>42</v>
       </c>
       <c r="E35" s="20"/>
-      <c r="G35" t="s">
-        <v>80</v>
+      <c r="G35" s="38" t="s">
+        <v>90</v>
       </c>
       <c r="H35" s="38" t="s">
         <v>90</v>
@@ -2209,20 +3074,29 @@
       <c r="I35" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="J35" s="38" t="s">
+      <c r="J35" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="L35" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="M35" t="s">
+        <v>80</v>
+      </c>
+      <c r="N35" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="K35" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="L35" s="38" t="s">
+      <c r="O35" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="M35" s="38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="36" spans="1:13">
+      <c r="P35" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="36" spans="1:16">
       <c r="A36" s="1">
         <v>27</v>
       </c>
@@ -2234,7 +3108,7 @@
       </c>
       <c r="E36" s="20"/>
       <c r="G36" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="H36" t="s">
         <v>84</v>
@@ -2242,20 +3116,29 @@
       <c r="I36" t="s">
         <v>84</v>
       </c>
-      <c r="J36" t="s">
+      <c r="J36" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="K36" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="L36" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="M36" t="s">
+        <v>81</v>
+      </c>
+      <c r="N36" t="s">
+        <v>81</v>
+      </c>
+      <c r="O36" t="s">
         <v>84</v>
       </c>
-      <c r="K36" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="L36" t="s">
-        <v>81</v>
-      </c>
-      <c r="M36" t="s">
+      <c r="P36" t="s">
         <v>84</v>
       </c>
     </row>
-    <row r="37" spans="1:13">
+    <row r="37" spans="1:16">
       <c r="A37" s="1">
         <v>28</v>
       </c>
@@ -2263,11 +3146,11 @@
         <v>26</v>
       </c>
       <c r="E37" s="20"/>
+      <c r="G37"/>
       <c r="H37"/>
-      <c r="I37"/>
-      <c r="L37"/>
-    </row>
-    <row r="38" spans="1:13">
+      <c r="N37"/>
+    </row>
+    <row r="38" spans="1:16">
       <c r="A38" s="1">
         <v>29</v>
       </c>
@@ -2276,7 +3159,7 @@
       </c>
       <c r="E38" s="20"/>
       <c r="G38" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="H38" t="s">
         <v>85</v>
@@ -2284,20 +3167,29 @@
       <c r="I38" t="s">
         <v>85</v>
       </c>
-      <c r="J38" t="s">
+      <c r="J38" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="K38" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="L38" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="M38" t="s">
+        <v>82</v>
+      </c>
+      <c r="N38" t="s">
+        <v>82</v>
+      </c>
+      <c r="O38" t="s">
         <v>85</v>
       </c>
-      <c r="K38" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="L38" t="s">
-        <v>82</v>
-      </c>
-      <c r="M38" t="s">
+      <c r="P38" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="39" spans="1:13">
+    <row r="39" spans="1:16">
       <c r="A39" s="1">
         <v>30</v>
       </c>
@@ -2305,26 +3197,35 @@
         <v>36</v>
       </c>
       <c r="E39" s="20"/>
+      <c r="G39" t="s">
+        <v>97</v>
+      </c>
       <c r="H39" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="I39" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="J39" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="K39" t="s">
-        <v>117</v>
+        <v>97</v>
       </c>
       <c r="L39" t="s">
-        <v>118</v>
-      </c>
-      <c r="M39" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13">
+        <v>97</v>
+      </c>
+      <c r="N39" t="s">
+        <v>98</v>
+      </c>
+      <c r="O39" t="s">
+        <v>97</v>
+      </c>
+      <c r="P39" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="40" spans="1:16">
       <c r="A40" s="1">
         <v>31</v>
       </c>
@@ -2347,20 +3248,29 @@
       <c r="I40" t="s">
         <v>44</v>
       </c>
-      <c r="J40" t="s">
-        <v>44</v>
+      <c r="J40" s="42" t="s">
+        <v>267</v>
       </c>
       <c r="K40" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="L40" t="s">
-        <v>91</v>
+        <v>277</v>
+      </c>
+      <c r="L40" s="42" t="s">
+        <v>291</v>
       </c>
       <c r="M40" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="41" spans="1:13">
+      <c r="N40" t="s">
+        <v>91</v>
+      </c>
+      <c r="O40" t="s">
+        <v>44</v>
+      </c>
+      <c r="P40" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="41" spans="1:16">
       <c r="A41" s="1">
         <v>32</v>
       </c>
@@ -2383,20 +3293,29 @@
       <c r="I41" t="s">
         <v>45</v>
       </c>
-      <c r="J41" t="s">
-        <v>45</v>
+      <c r="J41" s="42" t="s">
+        <v>269</v>
       </c>
       <c r="K41" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="L41" t="s">
-        <v>92</v>
+        <v>278</v>
+      </c>
+      <c r="L41" s="42" t="s">
+        <v>278</v>
       </c>
       <c r="M41" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="42" spans="1:13">
+      <c r="N41" t="s">
+        <v>92</v>
+      </c>
+      <c r="O41" t="s">
+        <v>45</v>
+      </c>
+      <c r="P41" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="42" spans="1:16">
       <c r="A42" s="1">
         <v>33</v>
       </c>
@@ -2407,24 +3326,33 @@
         <v>53</v>
       </c>
       <c r="E42" s="20"/>
+      <c r="G42" s="43" t="s">
+        <v>99</v>
+      </c>
       <c r="H42" s="43" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="I42" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="J42" s="43" t="s">
-        <v>119</v>
+        <v>99</v>
+      </c>
+      <c r="J42" s="42" t="s">
+        <v>279</v>
       </c>
       <c r="K42" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="L42"/>
-      <c r="M42" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13">
+        <v>280</v>
+      </c>
+      <c r="L42" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="N42"/>
+      <c r="O42" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="P42" s="43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="43" spans="1:16">
       <c r="A43" s="1">
         <v>34</v>
       </c>
@@ -2435,55 +3363,75 @@
         <v>54</v>
       </c>
       <c r="E43" s="20"/>
-      <c r="G43" t="s">
+      <c r="G43" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="H43" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I43" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="J43" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="K43" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="L43" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="M43" t="s">
         <v>83</v>
       </c>
-      <c r="H43" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="I43" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="J43" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="K43" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="L43" t="s">
+      <c r="N43" t="s">
         <v>83</v>
       </c>
-      <c r="M43" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13">
+      <c r="O43" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="P43" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="44" spans="1:16">
       <c r="A44" s="1">
         <v>35</v>
       </c>
-      <c r="B44" s="7"/>
+      <c r="B44" s="7" t="s">
+        <v>226</v>
+      </c>
       <c r="C44" s="36" t="s">
         <v>41</v>
       </c>
       <c r="E44" s="20"/>
+      <c r="G44" s="43" t="s">
+        <v>99</v>
+      </c>
       <c r="H44" s="43" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="I44" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="J44" s="43" t="s">
-        <v>119</v>
+        <v>99</v>
+      </c>
+      <c r="J44" s="42" t="s">
+        <v>283</v>
       </c>
       <c r="K44" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="L44"/>
-      <c r="M44" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="45" spans="1:13">
+        <v>284</v>
+      </c>
+      <c r="L44" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="N44"/>
+      <c r="O44" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="P44" s="43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="45" spans="1:16">
       <c r="A45" s="1">
         <v>36</v>
       </c>
@@ -2491,11 +3439,13 @@
         <v>40</v>
       </c>
       <c r="E45" s="20"/>
+      <c r="G45"/>
       <c r="H45"/>
-      <c r="I45"/>
-      <c r="L45"/>
-    </row>
-    <row r="46" spans="1:13">
+      <c r="K45" s="42"/>
+      <c r="L45" s="42"/>
+      <c r="N45"/>
+    </row>
+    <row r="46" spans="1:16">
       <c r="A46" s="1">
         <v>37</v>
       </c>
@@ -2503,11 +3453,11 @@
         <v>39</v>
       </c>
       <c r="E46" s="20"/>
+      <c r="G46"/>
       <c r="H46"/>
-      <c r="I46"/>
-      <c r="L46"/>
-    </row>
-    <row r="47" spans="1:13">
+      <c r="N46"/>
+    </row>
+    <row r="47" spans="1:16">
       <c r="A47" s="1">
         <v>38</v>
       </c>
@@ -2515,11 +3465,17 @@
         <v>26</v>
       </c>
       <c r="E47" s="20"/>
+      <c r="G47"/>
       <c r="H47"/>
-      <c r="I47"/>
-      <c r="L47"/>
-    </row>
-    <row r="48" spans="1:13">
+      <c r="K47" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="L47" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="N47"/>
+    </row>
+    <row r="48" spans="1:16">
       <c r="A48" s="1">
         <v>39</v>
       </c>
@@ -2528,7 +3484,7 @@
       </c>
       <c r="E48" s="20"/>
     </row>
-    <row r="49" spans="1:13" ht="18.75" thickBot="1">
+    <row r="49" spans="1:16" ht="18.75" thickBot="1">
       <c r="A49" s="1">
         <v>40</v>
       </c>
@@ -2539,77 +3495,102 @@
       <c r="D49" s="24"/>
       <c r="E49" s="23"/>
     </row>
-    <row r="50" spans="1:13" ht="18.75" thickBot="1">
+    <row r="50" spans="1:16" ht="18.75" thickBot="1">
       <c r="B50" s="2"/>
-      <c r="M50" s="42" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="18.75" thickBot="1">
+      <c r="O50" s="42" t="s">
+        <v>121</v>
+      </c>
+      <c r="P50" s="42"/>
+    </row>
+    <row r="51" spans="1:16" ht="18.75" thickBot="1">
       <c r="B51" s="40" t="s">
         <v>26</v>
       </c>
+      <c r="G51" t="s">
+        <v>286</v>
+      </c>
       <c r="H51" t="s">
-        <v>99</v>
+        <v>286</v>
       </c>
       <c r="I51" t="s">
-        <v>99</v>
+        <v>286</v>
       </c>
       <c r="J51" t="s">
-        <v>99</v>
+        <v>286</v>
       </c>
       <c r="K51" t="s">
-        <v>99</v>
-      </c>
-      <c r="M51" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="18.75" thickBot="1">
+        <v>286</v>
+      </c>
+      <c r="L51" t="s">
+        <v>286</v>
+      </c>
+      <c r="O51" t="s">
+        <v>286</v>
+      </c>
+      <c r="P51" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="52" spans="1:16" ht="18.75" thickBot="1">
       <c r="B52" s="41" t="s">
-        <v>110</v>
+        <v>95</v>
+      </c>
+      <c r="G52" t="s">
+        <v>287</v>
       </c>
       <c r="H52" t="s">
-        <v>100</v>
+        <v>287</v>
       </c>
       <c r="I52" t="s">
-        <v>100</v>
+        <v>287</v>
       </c>
       <c r="J52" t="s">
-        <v>100</v>
+        <v>287</v>
       </c>
       <c r="K52" t="s">
-        <v>100</v>
-      </c>
-      <c r="M52" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="18.75" thickBot="1">
+        <v>287</v>
+      </c>
+      <c r="L52" t="s">
+        <v>287</v>
+      </c>
+      <c r="O52" t="s">
+        <v>287</v>
+      </c>
+      <c r="P52" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="53" spans="1:16" ht="18.75" thickBot="1">
       <c r="B53" s="40" t="s">
         <v>26</v>
       </c>
-      <c r="J53" t="s">
-        <v>107</v>
-      </c>
-      <c r="M53" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="18.75" thickBot="1">
+      <c r="I53" t="s">
+        <v>288</v>
+      </c>
+      <c r="O53" t="s">
+        <v>288</v>
+      </c>
+      <c r="P53" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="54" spans="1:16" ht="18.75" thickBot="1">
       <c r="B54" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="J54" t="s">
-        <v>108</v>
-      </c>
-      <c r="M54" t="s">
-        <v>108</v>
+        <v>96</v>
+      </c>
+      <c r="I54" t="s">
+        <v>289</v>
+      </c>
+      <c r="O54" t="s">
+        <v>289</v>
+      </c>
+      <c r="P54" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="I21:I28">
-    <sortCondition descending="1" ref="I21:I28"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="H21:H28">
+    <sortCondition descending="1" ref="H21:H28"/>
   </sortState>
   <mergeCells count="2">
     <mergeCell ref="B1:E1"/>
@@ -2622,11 +3603,1157 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22879F06-826D-4665-AFBE-58D1FA19CBEA}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:K45"/>
+  <sheetFormatPr defaultColWidth="11.08984375" defaultRowHeight="18"/>
+  <cols>
+    <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="18.6328125" customWidth="1"/>
+    <col min="5" max="6" width="18.6328125" style="1" customWidth="1"/>
+    <col min="7" max="10" width="18.6328125" customWidth="1"/>
+    <col min="11" max="11" width="21.453125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:11" ht="18.75" thickBot="1">
+      <c r="C1" s="30" t="s">
+        <v>245</v>
+      </c>
+      <c r="E1" s="30" t="s">
+        <v>102</v>
+      </c>
+      <c r="F1" s="30" t="s">
+        <v>101</v>
+      </c>
+      <c r="G1" s="30" t="s">
+        <v>94</v>
+      </c>
+      <c r="H1" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="I1" s="30" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="30" t="s">
+        <v>128</v>
+      </c>
+      <c r="K1" s="30" t="s">
+        <v>245</v>
+      </c>
+    </row>
+    <row r="2" spans="1:11">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="25" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E2" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F2" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G2" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="H2" t="s">
+        <v>86</v>
+      </c>
+      <c r="I2" t="s">
+        <v>86</v>
+      </c>
+      <c r="J2" t="s">
+        <v>86</v>
+      </c>
+      <c r="K2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11">
+      <c r="A3" s="7">
+        <v>2</v>
+      </c>
+      <c r="B3" s="32" t="s">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>87</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G3" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="H3" t="s">
+        <v>87</v>
+      </c>
+      <c r="I3" t="s">
+        <v>87</v>
+      </c>
+      <c r="J3" t="s">
+        <v>87</v>
+      </c>
+      <c r="K3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="7">
+        <v>3</v>
+      </c>
+      <c r="B4" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4"/>
+      <c r="F4"/>
+      <c r="G4" s="42"/>
+    </row>
+    <row r="5" spans="1:11">
+      <c r="A5" s="7">
+        <v>4</v>
+      </c>
+      <c r="B5" s="32" t="s">
+        <v>2</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="E5" t="s">
+        <v>106</v>
+      </c>
+      <c r="F5" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="I5" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="J5" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="K5" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11">
+      <c r="A6" s="7">
+        <v>5</v>
+      </c>
+      <c r="B6" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="E6" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" t="s">
+        <v>107</v>
+      </c>
+      <c r="G6" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="H6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="I6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="J6" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="K6" s="38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11">
+      <c r="A7" s="7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="G7" s="42" t="s">
+        <v>250</v>
+      </c>
+      <c r="H7" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="I7" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="J7" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="K7" s="38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11">
+      <c r="A8" s="7">
+        <v>7</v>
+      </c>
+      <c r="B8" s="32" t="s">
+        <v>5</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>252</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="G8" s="42" t="s">
+        <v>251</v>
+      </c>
+      <c r="H8" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="J8" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="K8" s="42" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="9" spans="1:11">
+      <c r="A9" s="7">
+        <v>8</v>
+      </c>
+      <c r="B9" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9"/>
+      <c r="F9"/>
+      <c r="G9" s="42"/>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" s="7">
+        <v>9</v>
+      </c>
+      <c r="B10" s="32" t="s">
+        <v>6</v>
+      </c>
+      <c r="C10" t="s">
+        <v>44</v>
+      </c>
+      <c r="E10" t="s">
+        <v>108</v>
+      </c>
+      <c r="F10" t="s">
+        <v>108</v>
+      </c>
+      <c r="G10" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="H10" t="s">
+        <v>44</v>
+      </c>
+      <c r="I10" t="s">
+        <v>44</v>
+      </c>
+      <c r="J10" t="s">
+        <v>44</v>
+      </c>
+      <c r="K10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" s="7">
+        <v>10</v>
+      </c>
+      <c r="B11" s="32" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" t="s">
+        <v>109</v>
+      </c>
+      <c r="F11" t="s">
+        <v>109</v>
+      </c>
+      <c r="G11" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="H11" t="s">
+        <v>45</v>
+      </c>
+      <c r="I11" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" t="s">
+        <v>45</v>
+      </c>
+      <c r="K11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" s="7">
+        <v>11</v>
+      </c>
+      <c r="B12" s="32" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="F12" t="s">
+        <v>110</v>
+      </c>
+      <c r="G12" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="H12" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="J12" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="K12" s="42" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11">
+      <c r="A13" s="7">
+        <v>12</v>
+      </c>
+      <c r="B13" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" t="s">
+        <v>111</v>
+      </c>
+      <c r="G13" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="H13" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="J13" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="K13" s="42" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11">
+      <c r="A14" s="7">
+        <v>13</v>
+      </c>
+      <c r="B14" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C14" s="42"/>
+      <c r="E14" s="42"/>
+      <c r="G14" s="42"/>
+      <c r="H14" s="42"/>
+      <c r="I14" s="42"/>
+      <c r="J14" s="42"/>
+      <c r="K14" s="42"/>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" s="7">
+        <v>14</v>
+      </c>
+      <c r="B15" s="32" t="s">
+        <v>10</v>
+      </c>
+      <c r="C15" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="E15" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F15" t="s">
+        <v>117</v>
+      </c>
+      <c r="G15" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="H15" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="I15" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="J15" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="K15" s="42" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="16" spans="1:11">
+      <c r="A16" s="7">
+        <v>15</v>
+      </c>
+      <c r="B16" s="32" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="F16" t="s">
+        <v>116</v>
+      </c>
+      <c r="G16" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="H16" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="I16" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="J16" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="K16" s="42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" s="7">
+        <v>16</v>
+      </c>
+      <c r="B17" s="32" t="s">
+        <v>12</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="F17" t="s">
+        <v>115</v>
+      </c>
+      <c r="G17" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="H17" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="I17" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="J17" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="K17" s="42" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" s="7">
+        <v>17</v>
+      </c>
+      <c r="B18" s="32" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="F18" t="s">
+        <v>114</v>
+      </c>
+      <c r="G18" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="H18" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="I18" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="J18" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="K18" s="42" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" s="7">
+        <v>18</v>
+      </c>
+      <c r="B19" s="35" t="s">
+        <v>26</v>
+      </c>
+      <c r="C19" s="42"/>
+      <c r="E19" s="42"/>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="42"/>
+      <c r="J19" s="42"/>
+      <c r="K19" s="42"/>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" s="7">
+        <v>19</v>
+      </c>
+      <c r="B20" s="32" t="s">
+        <v>14</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="F20" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="H20" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="J20" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="K20" s="42" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" ht="18.75" thickBot="1">
+      <c r="A21" s="8">
+        <v>20</v>
+      </c>
+      <c r="B21" s="26" t="s">
+        <v>15</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="F21" t="s">
+        <v>112</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="H21" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="I21" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="J21" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="K21" s="42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" s="5" customFormat="1" ht="18.75" thickBot="1">
+      <c r="A22" s="3"/>
+      <c r="B22" s="4"/>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" s="1">
+        <v>21</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>25</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="E23" t="s">
+        <v>86</v>
+      </c>
+      <c r="F23" t="s">
+        <v>86</v>
+      </c>
+      <c r="G23" t="s">
+        <v>86</v>
+      </c>
+      <c r="H23" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="J23" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="K23" s="42" t="s">
+        <v>255</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" s="1">
+        <v>22</v>
+      </c>
+      <c r="B24" s="28" t="s">
+        <v>24</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="E24" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" t="s">
+        <v>87</v>
+      </c>
+      <c r="G24" t="s">
+        <v>87</v>
+      </c>
+      <c r="H24" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="I24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="J24" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="K24" s="42" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" s="1">
+        <v>23</v>
+      </c>
+      <c r="B25" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E25"/>
+      <c r="F25"/>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" s="1">
+        <v>24</v>
+      </c>
+      <c r="B26" s="28" t="s">
+        <v>23</v>
+      </c>
+      <c r="C26" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E26" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="F26" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="G26" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="H26" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="I26" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="J26" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="K26" s="42" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" s="1">
+        <v>25</v>
+      </c>
+      <c r="B27" s="28" t="s">
+        <v>22</v>
+      </c>
+      <c r="C27" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="E27" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="G27" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="H27" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="I27" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="J27" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="K27" s="42" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" s="1">
+        <v>26</v>
+      </c>
+      <c r="B28" s="28" t="s">
+        <v>21</v>
+      </c>
+      <c r="C28" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="E28" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="F28" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="G28" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="H28" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="I28" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="J28" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="K28" s="42" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" s="1">
+        <v>27</v>
+      </c>
+      <c r="B29" s="28" t="s">
+        <v>20</v>
+      </c>
+      <c r="C29" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E29" t="s">
+        <v>84</v>
+      </c>
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+      <c r="G29" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" s="42" t="s">
+        <v>273</v>
+      </c>
+      <c r="I29" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="J29" s="42" t="s">
+        <v>274</v>
+      </c>
+      <c r="K29" s="42" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" s="1">
+        <v>28</v>
+      </c>
+      <c r="B30" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30"/>
+      <c r="F30"/>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" s="1">
+        <v>29</v>
+      </c>
+      <c r="B31" s="28" t="s">
+        <v>19</v>
+      </c>
+      <c r="C31" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="E31" t="s">
+        <v>85</v>
+      </c>
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+      <c r="G31" t="s">
+        <v>85</v>
+      </c>
+      <c r="H31" s="42" t="s">
+        <v>275</v>
+      </c>
+      <c r="I31" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="J31" s="42" t="s">
+        <v>276</v>
+      </c>
+      <c r="K31" s="42" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" s="1">
+        <v>30</v>
+      </c>
+      <c r="B32" s="10" t="s">
+        <v>36</v>
+      </c>
+      <c r="C32" t="s">
+        <v>97</v>
+      </c>
+      <c r="E32" t="s">
+        <v>97</v>
+      </c>
+      <c r="F32" t="s">
+        <v>97</v>
+      </c>
+      <c r="G32" t="s">
+        <v>97</v>
+      </c>
+      <c r="H32" t="s">
+        <v>97</v>
+      </c>
+      <c r="I32" t="s">
+        <v>97</v>
+      </c>
+      <c r="J32" t="s">
+        <v>97</v>
+      </c>
+      <c r="K32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11">
+      <c r="A33" s="1">
+        <v>31</v>
+      </c>
+      <c r="B33" s="28" t="s">
+        <v>18</v>
+      </c>
+      <c r="C33" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="E33" t="s">
+        <v>44</v>
+      </c>
+      <c r="F33" t="s">
+        <v>44</v>
+      </c>
+      <c r="G33" t="s">
+        <v>44</v>
+      </c>
+      <c r="H33" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="I33" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="J33" s="42" t="s">
+        <v>277</v>
+      </c>
+      <c r="K33" s="42" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="34" spans="1:11">
+      <c r="A34" s="1">
+        <v>32</v>
+      </c>
+      <c r="B34" s="28" t="s">
+        <v>17</v>
+      </c>
+      <c r="C34" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="E34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F34" t="s">
+        <v>45</v>
+      </c>
+      <c r="G34" t="s">
+        <v>45</v>
+      </c>
+      <c r="H34" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="I34" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="J34" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="K34" s="42" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="35" spans="1:11">
+      <c r="A35" s="1">
+        <v>33</v>
+      </c>
+      <c r="B35" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="C35" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="E35" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G35" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="H35" s="42" t="s">
+        <v>279</v>
+      </c>
+      <c r="I35" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="J35" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="K35" s="42" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="36" spans="1:11">
+      <c r="A36" s="1">
+        <v>34</v>
+      </c>
+      <c r="B36" s="28" t="s">
+        <v>16</v>
+      </c>
+      <c r="C36" s="42" t="s">
+        <v>282</v>
+      </c>
+      <c r="E36" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F36" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G36" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="H36" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="I36" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="J36" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="K36" s="42" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="37" spans="1:11">
+      <c r="A37" s="1">
+        <v>35</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>226</v>
+      </c>
+      <c r="C37" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="E37" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="F37" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="G37" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="H37" s="42" t="s">
+        <v>283</v>
+      </c>
+      <c r="I37" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="J37" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="K37" s="42" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="38" spans="1:11">
+      <c r="A38" s="1">
+        <v>36</v>
+      </c>
+      <c r="B38" s="15" t="s">
+        <v>40</v>
+      </c>
+      <c r="C38" s="42"/>
+      <c r="E38"/>
+      <c r="F38"/>
+      <c r="I38" s="42" t="s">
+        <v>130</v>
+      </c>
+      <c r="J38" s="44" t="s">
+        <v>129</v>
+      </c>
+      <c r="K38" s="42"/>
+    </row>
+    <row r="39" spans="1:11">
+      <c r="A39" s="1">
+        <v>37</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="E39"/>
+      <c r="F39"/>
+    </row>
+    <row r="40" spans="1:11">
+      <c r="A40" s="1">
+        <v>38</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>26</v>
+      </c>
+      <c r="C40" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="E40"/>
+      <c r="F40"/>
+      <c r="I40" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="J40" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="K40" s="42" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="41" spans="1:11">
+      <c r="A41" s="1">
+        <v>39</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="42" spans="1:11" ht="18.75" thickBot="1">
+      <c r="A42" s="1">
+        <v>40</v>
+      </c>
+      <c r="B42" s="14" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11">
+      <c r="C44" t="s">
+        <v>286</v>
+      </c>
+      <c r="I44" t="s">
+        <v>286</v>
+      </c>
+      <c r="J44" t="s">
+        <v>286</v>
+      </c>
+      <c r="K44" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11">
+      <c r="C45" t="s">
+        <v>287</v>
+      </c>
+      <c r="I45" t="s">
+        <v>287</v>
+      </c>
+      <c r="J45" t="s">
+        <v>287</v>
+      </c>
+      <c r="K45" t="s">
+        <v>287</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup scale="53" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C3381470-3B61-4846-8AC0-7CE9B6B52A8A}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultColWidth="11.08984375" defaultRowHeight="18"/>
   <cols>
     <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
@@ -2634,20 +4761,24 @@
     <col min="3" max="3" width="32.7265625" style="1" customWidth="1"/>
     <col min="4" max="4" width="20.26953125" style="1" customWidth="1"/>
     <col min="5" max="5" width="24.26953125" customWidth="1"/>
+    <col min="6" max="6" width="23.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" thickBot="1">
+    <row r="1" spans="1:6" ht="18.75" thickBot="1">
       <c r="C1" s="30" t="s">
-        <v>93</v>
+        <v>122</v>
       </c>
       <c r="D1" s="30" t="s">
-        <v>127</v>
+        <v>103</v>
       </c>
       <c r="E1" s="30" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="2" spans="1:5">
+      <c r="F1" s="30" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
       <c r="A2" s="6">
         <v>1</v>
       </c>
@@ -2655,16 +4786,19 @@
         <v>0</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="D2" t="s">
         <v>78</v>
       </c>
       <c r="E2" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5">
+        <v>118</v>
+      </c>
+      <c r="F2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
       <c r="A3" s="7">
         <v>2</v>
       </c>
@@ -2672,16 +4806,19 @@
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="D3" t="s">
         <v>79</v>
       </c>
       <c r="E3" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5">
+        <v>119</v>
+      </c>
+      <c r="F3" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
       <c r="A4" s="7">
         <v>3</v>
       </c>
@@ -2691,15 +4828,15 @@
       <c r="C4"/>
       <c r="D4"/>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:6">
       <c r="A5" s="7">
         <v>4</v>
       </c>
       <c r="B5" s="32" t="s">
         <v>2</v>
       </c>
-      <c r="C5" t="s">
-        <v>80</v>
+      <c r="C5" s="38" t="s">
+        <v>88</v>
       </c>
       <c r="D5" t="s">
         <v>80</v>
@@ -2707,59 +4844,71 @@
       <c r="E5" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
+      <c r="F5" s="38" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
       <c r="A6" s="7">
         <v>5</v>
       </c>
       <c r="B6" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="C6" t="s">
-        <v>81</v>
+      <c r="C6" s="38" t="s">
+        <v>89</v>
       </c>
       <c r="D6" t="s">
         <v>63</v>
       </c>
       <c r="E6" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
+        <v>120</v>
+      </c>
+      <c r="F6" s="38" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
       <c r="A7" s="7">
         <v>6</v>
       </c>
       <c r="B7" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="43" t="s">
-        <v>119</v>
+      <c r="C7" s="38" t="s">
+        <v>90</v>
       </c>
       <c r="D7" t="s">
         <v>64</v>
       </c>
       <c r="E7" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
+        <v>99</v>
+      </c>
+      <c r="F7" s="38" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
       <c r="A8" s="7">
         <v>7</v>
       </c>
       <c r="B8" s="32" t="s">
         <v>5</v>
       </c>
-      <c r="C8" s="43" t="s">
-        <v>119</v>
+      <c r="C8" t="s">
+        <v>124</v>
       </c>
       <c r="D8" t="s">
         <v>65</v>
       </c>
       <c r="E8" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
+        <v>99</v>
+      </c>
+      <c r="F8" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
       <c r="A9" s="7">
         <v>8</v>
       </c>
@@ -2769,7 +4918,7 @@
       <c r="C9"/>
       <c r="D9"/>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:6">
       <c r="A10" s="7">
         <v>9</v>
       </c>
@@ -2777,7 +4926,7 @@
         <v>6</v>
       </c>
       <c r="C10" t="s">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="D10" t="s">
         <v>73</v>
@@ -2785,8 +4934,11 @@
       <c r="E10" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="11" spans="1:5">
+      <c r="F10" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
       <c r="A11" s="7">
         <v>10</v>
       </c>
@@ -2794,7 +4946,7 @@
         <v>7</v>
       </c>
       <c r="C11" t="s">
-        <v>75</v>
+        <v>45</v>
       </c>
       <c r="D11" t="s">
         <v>66</v>
@@ -2802,8 +4954,11 @@
       <c r="E11" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="1:5">
+      <c r="F11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
       <c r="A12" s="7">
         <v>11</v>
       </c>
@@ -2811,16 +4966,19 @@
         <v>8</v>
       </c>
       <c r="C12" t="s">
-        <v>120</v>
+        <v>256</v>
       </c>
       <c r="D12" t="s">
         <v>67</v>
       </c>
       <c r="E12" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
+        <v>256</v>
+      </c>
+      <c r="F12" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
       <c r="A13" s="7">
         <v>12</v>
       </c>
@@ -2828,16 +4986,19 @@
         <v>9</v>
       </c>
       <c r="C13" t="s">
-        <v>121</v>
+        <v>258</v>
       </c>
       <c r="D13" t="s">
         <v>68</v>
       </c>
       <c r="E13" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
+        <v>258</v>
+      </c>
+      <c r="F13" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
       <c r="A14" s="7">
         <v>13</v>
       </c>
@@ -2847,7 +5008,7 @@
       <c r="C14"/>
       <c r="D14"/>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:6">
       <c r="A15" s="7">
         <v>14</v>
       </c>
@@ -2855,16 +5016,19 @@
         <v>10</v>
       </c>
       <c r="C15" t="s">
-        <v>122</v>
+        <v>261</v>
       </c>
       <c r="D15" t="s">
         <v>69</v>
       </c>
       <c r="E15" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
+        <v>261</v>
+      </c>
+      <c r="F15" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
       <c r="A16" s="7">
         <v>15</v>
       </c>
@@ -2872,16 +5036,19 @@
         <v>11</v>
       </c>
       <c r="C16" t="s">
-        <v>123</v>
+        <v>264</v>
       </c>
       <c r="D16" t="s">
         <v>70</v>
       </c>
       <c r="E16" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
+        <v>264</v>
+      </c>
+      <c r="F16" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6">
       <c r="A17" s="7">
         <v>16</v>
       </c>
@@ -2889,16 +5056,19 @@
         <v>12</v>
       </c>
       <c r="C17" t="s">
-        <v>151</v>
+        <v>266</v>
       </c>
       <c r="D17" t="s">
         <v>71</v>
       </c>
       <c r="E17" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
+        <v>266</v>
+      </c>
+      <c r="F17" t="s">
+        <v>266</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
       <c r="A18" s="7">
         <v>17</v>
       </c>
@@ -2906,16 +5076,19 @@
         <v>13</v>
       </c>
       <c r="C18" t="s">
-        <v>152</v>
+        <v>268</v>
       </c>
       <c r="D18" t="s">
         <v>72</v>
       </c>
       <c r="E18" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
+        <v>268</v>
+      </c>
+      <c r="F18" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
       <c r="A19" s="7">
         <v>18</v>
       </c>
@@ -2925,7 +5098,7 @@
       <c r="C19"/>
       <c r="D19"/>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:6">
       <c r="A20" s="7">
         <v>19</v>
       </c>
@@ -2933,16 +5106,19 @@
         <v>14</v>
       </c>
       <c r="C20" t="s">
-        <v>155</v>
+        <v>290</v>
       </c>
       <c r="D20" t="s">
         <v>74</v>
       </c>
       <c r="E20" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" ht="18.75" thickBot="1">
+        <v>270</v>
+      </c>
+      <c r="F20" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" ht="18.75" thickBot="1">
       <c r="A21" s="8">
         <v>20</v>
       </c>
@@ -2950,28 +5126,31 @@
         <v>15</v>
       </c>
       <c r="C21" s="42" t="s">
-        <v>153</v>
+        <v>272</v>
       </c>
       <c r="D21" t="s">
         <v>75</v>
       </c>
       <c r="E21" s="42" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" s="5" customFormat="1" ht="18.75" thickBot="1">
+        <v>272</v>
+      </c>
+      <c r="F21" s="42" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" s="5" customFormat="1" ht="18.75" thickBot="1">
       <c r="A22" s="3"/>
       <c r="B22" s="4"/>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:6">
       <c r="A23" s="1">
         <v>21</v>
       </c>
       <c r="B23" s="27" t="s">
         <v>25</v>
       </c>
-      <c r="C23" t="s">
-        <v>86</v>
+      <c r="C23" s="1" t="s">
+        <v>42</v>
       </c>
       <c r="D23" t="s">
         <v>86</v>
@@ -2979,16 +5158,19 @@
       <c r="E23" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
+      <c r="F23" s="1" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
       <c r="A24" s="1">
         <v>22</v>
       </c>
       <c r="B24" s="28" t="s">
         <v>24</v>
       </c>
-      <c r="C24" t="s">
-        <v>87</v>
+      <c r="C24" s="1" t="s">
+        <v>43</v>
       </c>
       <c r="D24" t="s">
         <v>87</v>
@@ -2996,8 +5178,11 @@
       <c r="E24" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:5">
+      <c r="F24" s="1" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
       <c r="A25" s="1">
         <v>23</v>
       </c>
@@ -3007,15 +5192,15 @@
       <c r="C25"/>
       <c r="D25"/>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:6">
       <c r="A26" s="1">
         <v>24</v>
       </c>
       <c r="B26" s="28" t="s">
         <v>23</v>
       </c>
-      <c r="C26" s="38" t="s">
-        <v>88</v>
+      <c r="C26" t="s">
+        <v>118</v>
       </c>
       <c r="D26" s="38" t="s">
         <v>88</v>
@@ -3023,16 +5208,19 @@
       <c r="E26" s="38" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:5">
+      <c r="F26" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" s="1">
         <v>25</v>
       </c>
       <c r="B27" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="C27" s="38" t="s">
-        <v>89</v>
+      <c r="C27" t="s">
+        <v>119</v>
       </c>
       <c r="D27" s="38" t="s">
         <v>89</v>
@@ -3040,16 +5228,19 @@
       <c r="E27" s="38" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
+      <c r="F27" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6">
       <c r="A28" s="1">
         <v>26</v>
       </c>
       <c r="B28" s="28" t="s">
         <v>21</v>
       </c>
-      <c r="C28" s="38" t="s">
-        <v>90</v>
+      <c r="C28" t="s">
+        <v>120</v>
       </c>
       <c r="D28" s="38" t="s">
         <v>90</v>
@@ -3057,8 +5248,11 @@
       <c r="E28" s="38" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="29" spans="1:5">
+      <c r="F28" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6">
       <c r="A29" s="1">
         <v>27</v>
       </c>
@@ -3074,8 +5268,11 @@
       <c r="E29" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="30" spans="1:5">
+      <c r="F29" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6">
       <c r="A30" s="1">
         <v>28</v>
       </c>
@@ -3085,7 +5282,7 @@
       <c r="C30"/>
       <c r="D30"/>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:6">
       <c r="A31" s="1">
         <v>29</v>
       </c>
@@ -3101,8 +5298,11 @@
       <c r="E31" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="32" spans="1:5">
+      <c r="F31" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6">
       <c r="A32" s="1">
         <v>30</v>
       </c>
@@ -3110,16 +5310,19 @@
         <v>36</v>
       </c>
       <c r="C32" t="s">
-        <v>118</v>
+        <v>97</v>
       </c>
       <c r="D32" t="s">
-        <v>118</v>
+        <v>98</v>
       </c>
       <c r="E32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
+        <v>97</v>
+      </c>
+      <c r="F32" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6">
       <c r="A33" s="1">
         <v>31</v>
       </c>
@@ -3127,7 +5330,7 @@
         <v>18</v>
       </c>
       <c r="C33" t="s">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="D33" t="s">
         <v>91</v>
@@ -3135,8 +5338,11 @@
       <c r="E33" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="34" spans="1:5">
+      <c r="F33" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6">
       <c r="A34" s="1">
         <v>32</v>
       </c>
@@ -3144,7 +5350,7 @@
         <v>17</v>
       </c>
       <c r="C34" t="s">
-        <v>45</v>
+        <v>75</v>
       </c>
       <c r="D34" t="s">
         <v>92</v>
@@ -3152,8 +5358,11 @@
       <c r="E34" t="s">
         <v>45</v>
       </c>
-    </row>
-    <row r="35" spans="1:5">
+      <c r="F34" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6">
       <c r="A35" s="1">
         <v>33</v>
       </c>
@@ -3161,40 +5370,51 @@
         <v>26</v>
       </c>
       <c r="C35" s="43" t="s">
-        <v>119</v>
+        <v>99</v>
       </c>
       <c r="D35"/>
       <c r="E35" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
+        <v>99</v>
+      </c>
+      <c r="F35" s="43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6">
       <c r="A36" s="1">
         <v>34</v>
       </c>
       <c r="B36" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="C36" s="43" t="s">
-        <v>119</v>
+      <c r="C36" t="s">
+        <v>80</v>
       </c>
       <c r="D36" t="s">
         <v>83</v>
       </c>
       <c r="E36" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
+        <v>99</v>
+      </c>
+      <c r="F36" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6">
       <c r="A37" s="1">
         <v>35</v>
       </c>
       <c r="B37" s="7"/>
-      <c r="C37"/>
+      <c r="C37" s="43" t="s">
+        <v>99</v>
+      </c>
       <c r="D37"/>
       <c r="E37" s="43"/>
-    </row>
-    <row r="38" spans="1:5">
+      <c r="F37" s="43" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6">
       <c r="A38" s="1">
         <v>36</v>
       </c>
@@ -3204,7 +5424,7 @@
       <c r="C38"/>
       <c r="D38"/>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:6">
       <c r="A39" s="1">
         <v>37</v>
       </c>
@@ -3214,7 +5434,7 @@
       <c r="C39"/>
       <c r="D39"/>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:6">
       <c r="A40" s="1">
         <v>38</v>
       </c>
@@ -3224,20 +5444,58 @@
       <c r="C40"/>
       <c r="D40"/>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:6">
       <c r="A41" s="1">
         <v>39</v>
       </c>
       <c r="B41" s="13" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" ht="18.75" thickBot="1">
+      <c r="C41"/>
+    </row>
+    <row r="42" spans="1:6" ht="18.75" thickBot="1">
       <c r="A42" s="1">
         <v>40</v>
       </c>
       <c r="B42" s="14" t="s">
         <v>37</v>
+      </c>
+      <c r="C42"/>
+    </row>
+    <row r="43" spans="1:6">
+      <c r="C43" s="42"/>
+      <c r="F43" s="42"/>
+    </row>
+    <row r="44" spans="1:6">
+      <c r="C44" t="s">
+        <v>286</v>
+      </c>
+      <c r="F44" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6">
+      <c r="C45" t="s">
+        <v>287</v>
+      </c>
+      <c r="F45" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6">
+      <c r="C46" t="s">
+        <v>288</v>
+      </c>
+      <c r="F46" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6">
+      <c r="C47" t="s">
+        <v>289</v>
+      </c>
+      <c r="F47" t="s">
+        <v>289</v>
       </c>
     </row>
   </sheetData>
@@ -3246,730 +5504,1775 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22879F06-826D-4665-AFBE-58D1FA19CBEA}">
-  <sheetPr>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:G42"/>
-  <sheetFormatPr defaultColWidth="11.08984375" defaultRowHeight="18"/>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2CCDCCD1-E885-4F68-B198-5EA70C835413}">
+  <dimension ref="A2:J90"/>
+  <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.81640625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="8.54296875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.36328125" customWidth="1"/>
-    <col min="5" max="5" width="26.6328125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.26953125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="24.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.453125" customWidth="1"/>
+    <col min="2" max="2" width="19.36328125" customWidth="1"/>
+    <col min="3" max="3" width="15.453125" customWidth="1"/>
+    <col min="4" max="4" width="19.36328125" customWidth="1"/>
+    <col min="5" max="5" width="13.26953125" customWidth="1"/>
+    <col min="6" max="6" width="15.54296875" customWidth="1"/>
+    <col min="7" max="7" width="13" customWidth="1"/>
+    <col min="8" max="8" width="9.54296875" customWidth="1"/>
+    <col min="9" max="10" width="16.453125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="18.75" thickBot="1">
-      <c r="C1" s="30" t="s">
-        <v>129</v>
-      </c>
-      <c r="E1" s="30" t="s">
+    <row r="2" spans="1:10" ht="18.75" thickBot="1"/>
+    <row r="3" spans="1:10">
+      <c r="A3" s="57" t="s">
+        <v>229</v>
+      </c>
+      <c r="B3" s="58"/>
+      <c r="C3" s="57" t="s">
+        <v>227</v>
+      </c>
+      <c r="D3" s="58"/>
+      <c r="E3" s="57" t="s">
+        <v>228</v>
+      </c>
+      <c r="F3" s="58"/>
+      <c r="G3" s="47"/>
+      <c r="H3" s="47"/>
+      <c r="I3" s="57" t="s">
+        <v>125</v>
+      </c>
+      <c r="J3" s="64"/>
+    </row>
+    <row r="4" spans="1:10" ht="18.75" thickBot="1">
+      <c r="A4" s="59" t="s">
         <v>126</v>
       </c>
-      <c r="F1" s="30" t="s">
-        <v>125</v>
-      </c>
-      <c r="G1" s="30" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="25" t="s">
-        <v>0</v>
-      </c>
-      <c r="C2" t="s">
-        <v>86</v>
-      </c>
-      <c r="E2" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F2" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G2" s="42" t="s">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="7">
-        <v>2</v>
-      </c>
-      <c r="B3" s="32" t="s">
-        <v>1</v>
-      </c>
-      <c r="C3" t="s">
-        <v>87</v>
-      </c>
-      <c r="E3" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F3" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G3" s="42" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="7">
-        <v>3</v>
-      </c>
-      <c r="B4" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E4"/>
-      <c r="F4"/>
-      <c r="G4" s="42"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="7">
-        <v>4</v>
-      </c>
-      <c r="B5" s="32" t="s">
-        <v>2</v>
-      </c>
-      <c r="C5" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="E5" t="s">
-        <v>130</v>
+      <c r="B4" s="60"/>
+      <c r="C4" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="F4" s="60"/>
+      <c r="G4" s="48"/>
+      <c r="H4" s="48"/>
+      <c r="I4" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="J4" s="63"/>
+    </row>
+    <row r="5" spans="1:10">
+      <c r="A5" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="B5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" t="s">
+        <v>133</v>
+      </c>
+      <c r="E5" s="42" t="s">
+        <v>246</v>
       </c>
       <c r="F5" t="s">
-        <v>130</v>
-      </c>
-      <c r="G5" s="42" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="7">
-        <v>5</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>3</v>
-      </c>
-      <c r="C6" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="E6" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>319</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
+      <c r="A6" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="B6" t="s">
+        <v>235</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="D6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E6" s="42" t="s">
+        <v>247</v>
+      </c>
+      <c r="F6" t="s">
+        <v>134</v>
+      </c>
+      <c r="G6" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>320</v>
+      </c>
+      <c r="I6" s="42" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
+      <c r="A7" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="B7" t="s">
+        <v>236</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="D7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E7" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="F7" t="s">
+        <v>135</v>
+      </c>
+      <c r="G7" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="H7" s="53" t="s">
+        <v>321</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
+      <c r="A8" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="B8" t="s">
+        <v>237</v>
+      </c>
+      <c r="C8" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="D8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E8" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="F8" t="s">
+        <v>136</v>
+      </c>
+      <c r="G8" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="H8" s="53" t="s">
+        <v>322</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
+      <c r="A9" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="B9" t="s">
         <v>131</v>
       </c>
-      <c r="F6" t="s">
+      <c r="C9" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="D9" t="s">
         <v>131</v>
       </c>
-      <c r="G6" s="42" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>4</v>
-      </c>
-      <c r="C7" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="E7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="G7" s="42" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="7">
-        <v>7</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="E8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="G8" s="42" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="7">
+      <c r="E9" s="42" t="s">
+        <v>286</v>
+      </c>
+      <c r="F9" t="s">
+        <v>131</v>
+      </c>
+      <c r="G9" s="46" t="s">
+        <v>292</v>
+      </c>
+      <c r="H9" s="53"/>
+      <c r="I9" s="42" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
+      <c r="A10" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="B10" s="45" t="s">
+        <v>243</v>
+      </c>
+      <c r="C10" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="D10" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="E10" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="F10" s="45" t="s">
+        <v>132</v>
+      </c>
+      <c r="G10" s="46" t="s">
+        <v>293</v>
+      </c>
+      <c r="H10" s="53"/>
+      <c r="I10" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="J10" s="45"/>
+    </row>
+    <row r="11" spans="1:10">
+      <c r="A11" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="B11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C11" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="D11" t="s">
+        <v>137</v>
+      </c>
+      <c r="E11" s="42" t="s">
+        <v>262</v>
+      </c>
+      <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="53" t="s">
+        <v>323</v>
+      </c>
+      <c r="I11" s="42" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
+      <c r="A12" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="B12" t="s">
+        <v>239</v>
+      </c>
+      <c r="C12" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="D12" t="s">
+        <v>138</v>
+      </c>
+      <c r="E12" s="42" t="s">
+        <v>259</v>
+      </c>
+      <c r="F12" t="s">
+        <v>223</v>
+      </c>
+      <c r="G12" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="H12" s="53" t="s">
+        <v>324</v>
+      </c>
+      <c r="I12" s="42" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
+      <c r="A13" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="B13" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" t="s">
+        <v>139</v>
+      </c>
+      <c r="E13" s="42" t="s">
+        <v>253</v>
+      </c>
+      <c r="F13" t="s">
+        <v>183</v>
+      </c>
+      <c r="G13" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="H13" s="53" t="s">
+        <v>325</v>
+      </c>
+      <c r="I13" s="42" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
+      <c r="A14" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="B14" t="s">
+        <v>241</v>
+      </c>
+      <c r="C14" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="D14" t="s">
+        <v>140</v>
+      </c>
+      <c r="E14" s="42" t="s">
+        <v>254</v>
+      </c>
+      <c r="H14" s="53" t="s">
+        <v>326</v>
+      </c>
+      <c r="I14" s="42" t="s">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
+      <c r="A16" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="B16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C16" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="E16" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="I16" s="42" t="s">
+        <v>255</v>
+      </c>
+      <c r="J16" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
+      <c r="A17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="B17" t="s">
+        <v>138</v>
+      </c>
+      <c r="C17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="E17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="I17" s="42" t="s">
+        <v>257</v>
+      </c>
+      <c r="J17" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
+      <c r="A18" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="B18" t="s">
+        <v>189</v>
+      </c>
+      <c r="C18" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="E18" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="I18" s="42" t="s">
+        <v>260</v>
+      </c>
+      <c r="J18" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
+      <c r="A19" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" t="s">
+        <v>244</v>
+      </c>
+      <c r="C19" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="E19" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="I19" s="42" t="s">
+        <v>263</v>
+      </c>
+      <c r="J19" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
+      <c r="A20" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="B20" t="s">
+        <v>131</v>
+      </c>
+      <c r="C20" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="E20" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="I20" s="42" t="s">
+        <v>288</v>
+      </c>
+      <c r="J20" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
+      <c r="A21" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="B21" s="45" t="s">
+        <v>242</v>
+      </c>
+      <c r="C21" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="E21" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="I21" s="42" t="s">
+        <v>289</v>
+      </c>
+      <c r="J21" s="45" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
+      <c r="A22" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="B22" t="s">
+        <v>191</v>
+      </c>
+      <c r="C22" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="E22" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="I22" s="42" t="s">
+        <v>265</v>
+      </c>
+      <c r="J22" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
+      <c r="A23" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="B23" t="s">
+        <v>74</v>
+      </c>
+      <c r="C23" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="E23" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="I23" s="42" t="s">
+        <v>267</v>
+      </c>
+      <c r="J23" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
+      <c r="A24" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="E24" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="I24" s="42" t="s">
+        <v>269</v>
+      </c>
+      <c r="J24" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
+      <c r="A25" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="B25" t="s">
+        <v>80</v>
+      </c>
+      <c r="C25" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="E25" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="I25" s="42" t="s">
+        <v>271</v>
+      </c>
+      <c r="J25" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
+      <c r="C26" s="42"/>
+      <c r="E26" s="42"/>
+    </row>
+    <row r="27" spans="1:10">
+      <c r="A27" s="42" t="s">
+        <v>291</v>
+      </c>
+      <c r="B27" t="s">
+        <v>80</v>
+      </c>
+      <c r="C27" s="42"/>
+      <c r="E27" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="F27" t="s">
+        <v>184</v>
+      </c>
+      <c r="G27" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="H27" s="45"/>
+    </row>
+    <row r="28" spans="1:10">
+      <c r="A28" s="42" t="s">
+        <v>278</v>
+      </c>
+      <c r="B28" t="s">
+        <v>233</v>
+      </c>
+      <c r="C28" s="42"/>
+      <c r="E28" s="42"/>
+    </row>
+    <row r="29" spans="1:10">
+      <c r="A29" s="42" t="s">
+        <v>280</v>
+      </c>
+      <c r="B29" t="s">
+        <v>225</v>
+      </c>
+      <c r="C29" s="42"/>
+      <c r="E29" s="42"/>
+    </row>
+    <row r="30" spans="1:10">
+      <c r="A30" s="42" t="s">
+        <v>284</v>
+      </c>
+      <c r="B30" s="65" t="s">
+        <v>231</v>
+      </c>
+      <c r="C30" t="s">
+        <v>226</v>
+      </c>
+      <c r="E30" s="42" t="s">
+        <v>246</v>
+      </c>
+      <c r="F30" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="G30" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="H30" s="46"/>
+      <c r="I30" s="42"/>
+      <c r="J30" s="45"/>
+    </row>
+    <row r="31" spans="1:10">
+      <c r="A31" s="42" t="s">
+        <v>281</v>
+      </c>
+      <c r="B31" s="66" t="s">
+        <v>226</v>
+      </c>
+      <c r="C31" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="E31" s="42" t="s">
+        <v>249</v>
+      </c>
+      <c r="F31" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="G31" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="H31" s="46"/>
+      <c r="I31" s="42"/>
+      <c r="J31" s="45"/>
+    </row>
+    <row r="32" spans="1:10">
+      <c r="A32" s="42" t="s">
+        <v>285</v>
+      </c>
+      <c r="B32" t="s">
+        <v>131</v>
+      </c>
+      <c r="E32" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="F32" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="G32" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="H32" s="46"/>
+      <c r="I32" s="42"/>
+      <c r="J32" s="45"/>
+    </row>
+    <row r="33" spans="1:10">
+      <c r="C33" s="42"/>
+      <c r="E33" s="42"/>
+      <c r="I33" s="42"/>
+      <c r="J33" s="45"/>
+    </row>
+    <row r="34" spans="1:10">
+      <c r="A34" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="B34" t="s">
+        <v>213</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="E34" s="42"/>
+      <c r="I34" s="42" t="s">
+        <v>193</v>
+      </c>
+      <c r="J34" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
+      <c r="A35" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="B35" t="s">
+        <v>131</v>
+      </c>
+      <c r="C35" s="42"/>
+      <c r="E35" s="42"/>
+      <c r="I35" s="42" t="s">
+        <v>194</v>
+      </c>
+      <c r="J35" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
+      <c r="A36" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="B36" s="45" t="s">
+        <v>214</v>
+      </c>
+      <c r="C36" s="42"/>
+      <c r="E36" s="42"/>
+      <c r="I36" s="42" t="s">
+        <v>195</v>
+      </c>
+      <c r="J36" s="45" t="s">
+        <v>214</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10" ht="18.75" thickBot="1"/>
+    <row r="38" spans="1:10" ht="18.75" thickBot="1">
+      <c r="A38" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="B38" s="62"/>
+      <c r="C38" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="D38" s="62"/>
+      <c r="E38" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="F38" s="62"/>
+      <c r="G38" s="49"/>
+      <c r="H38" s="49"/>
+      <c r="I38" s="61" t="s">
+        <v>127</v>
+      </c>
+      <c r="J38" s="62"/>
+    </row>
+    <row r="39" spans="1:10">
+      <c r="A39" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="B39" t="s">
+        <v>131</v>
+      </c>
+      <c r="C39" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" t="s">
+        <v>131</v>
+      </c>
+      <c r="E39" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="F39" t="s">
+        <v>131</v>
+      </c>
+      <c r="I39" s="42" t="s">
+        <v>196</v>
+      </c>
+      <c r="J39" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
+      <c r="A40" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="B40" s="45" t="s">
+        <v>230</v>
+      </c>
+      <c r="C40" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="D40" t="s">
+        <v>131</v>
+      </c>
+      <c r="E40" s="46" t="s">
+        <v>142</v>
+      </c>
+      <c r="F40" t="s">
+        <v>131</v>
+      </c>
+      <c r="I40" s="42" t="s">
+        <v>197</v>
+      </c>
+      <c r="J40" s="45" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
+      <c r="A41" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="B41" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="C41" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="D41" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E41" s="46" t="s">
+        <v>143</v>
+      </c>
+      <c r="F41" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="G41" s="45"/>
+      <c r="H41" s="45"/>
+      <c r="I41" s="42" t="s">
+        <v>198</v>
+      </c>
+      <c r="J41" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
+      <c r="A42" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="B42" s="45" t="s">
+        <v>231</v>
+      </c>
+      <c r="C42" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="D42" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E42" s="46" t="s">
+        <v>144</v>
+      </c>
+      <c r="F42" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="G42" s="45"/>
+      <c r="H42" s="45"/>
+    </row>
+    <row r="43" spans="1:10">
+      <c r="A43" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="B43" s="45" t="s">
+        <v>232</v>
+      </c>
+      <c r="C43" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" t="s">
+        <v>134</v>
+      </c>
+      <c r="E43" s="46" t="s">
+        <v>145</v>
+      </c>
+      <c r="F43" t="s">
+        <v>134</v>
+      </c>
+      <c r="I43" s="42" t="s">
+        <v>199</v>
+      </c>
+      <c r="J43" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
+      <c r="A44" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="B44" t="s">
+        <v>233</v>
+      </c>
+      <c r="C44" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="D44" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="46" t="s">
+        <v>146</v>
+      </c>
+      <c r="F44" t="s">
+        <v>133</v>
+      </c>
+      <c r="I44" s="42" t="s">
+        <v>200</v>
+      </c>
+      <c r="J44" s="45" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
+      <c r="A45" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="B45" t="s">
+        <v>183</v>
+      </c>
+      <c r="C45" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="D45" t="s">
+        <v>136</v>
+      </c>
+      <c r="E45" s="46" t="s">
+        <v>147</v>
+      </c>
+      <c r="F45" t="s">
+        <v>136</v>
+      </c>
+      <c r="I45" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="J45" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
+      <c r="A46" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" t="s">
+        <v>182</v>
+      </c>
+      <c r="C46" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="D46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="46" t="s">
+        <v>148</v>
+      </c>
+      <c r="F46" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
+      <c r="A47" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="B47" t="s">
+        <v>234</v>
+      </c>
+      <c r="C47" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="D47" t="s">
+        <v>182</v>
+      </c>
+      <c r="E47" s="46" t="s">
+        <v>149</v>
+      </c>
+      <c r="F47" t="s">
+        <v>182</v>
+      </c>
+      <c r="I47" s="42" t="s">
+        <v>202</v>
+      </c>
+      <c r="J47" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
+      <c r="A48" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B48" t="s">
+        <v>235</v>
+      </c>
+      <c r="C48" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="D48" t="s">
+        <v>182</v>
+      </c>
+      <c r="E48" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="F48" t="s">
+        <v>182</v>
+      </c>
+      <c r="I48" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="J48" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
+      <c r="A49" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="B49" t="s">
+        <v>236</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
+        <v>183</v>
+      </c>
+      <c r="E49" s="46" t="s">
+        <v>151</v>
+      </c>
+      <c r="F49" t="s">
+        <v>183</v>
+      </c>
+      <c r="I49" s="42" t="s">
+        <v>204</v>
+      </c>
+      <c r="J49" s="45" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
+      <c r="A50" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="B50" t="s">
+        <v>237</v>
+      </c>
+      <c r="C50" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="D50" t="s">
+        <v>182</v>
+      </c>
+      <c r="E50" s="46" t="s">
+        <v>152</v>
+      </c>
+      <c r="F50" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
+      <c r="A51" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="B51" t="s">
+        <v>238</v>
+      </c>
+      <c r="C51" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="D51" t="s">
+        <v>131</v>
+      </c>
+      <c r="E51" s="46" t="s">
+        <v>153</v>
+      </c>
+      <c r="F51" t="s">
+        <v>131</v>
+      </c>
+      <c r="I51" s="44" t="s">
+        <v>205</v>
+      </c>
+      <c r="J51" s="45" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="A52" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="B52" t="s">
+        <v>239</v>
+      </c>
+      <c r="C52" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" t="s">
+        <v>184</v>
+      </c>
+      <c r="E52" s="46" t="s">
+        <v>154</v>
+      </c>
+      <c r="F52" t="s">
+        <v>184</v>
+      </c>
+      <c r="I52" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="J52" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="A53" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="B53" t="s">
+        <v>240</v>
+      </c>
+      <c r="C53" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="D53" t="s">
+        <v>182</v>
+      </c>
+      <c r="E53" s="46" t="s">
+        <v>155</v>
+      </c>
+      <c r="F53" t="s">
+        <v>182</v>
+      </c>
+      <c r="I53" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="J53" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="A54" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="B54" t="s">
+        <v>241</v>
+      </c>
+      <c r="C54" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="D54" t="s">
+        <v>182</v>
+      </c>
+      <c r="E54" s="46" t="s">
+        <v>156</v>
+      </c>
+      <c r="F54" t="s">
+        <v>182</v>
+      </c>
+      <c r="I54" s="44" t="s">
+        <v>208</v>
+      </c>
+      <c r="J54" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="A55" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="B55" t="s">
+        <v>182</v>
+      </c>
+      <c r="C55" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="D55" t="s">
+        <v>182</v>
+      </c>
+      <c r="E55" s="46" t="s">
+        <v>157</v>
+      </c>
+      <c r="F55" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="A56" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="B56" t="s">
+        <v>182</v>
+      </c>
+      <c r="C56" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="D56" t="s">
+        <v>182</v>
+      </c>
+      <c r="E56" s="46" t="s">
+        <v>158</v>
+      </c>
+      <c r="F56" t="s">
+        <v>182</v>
+      </c>
+      <c r="I56" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="J56" s="45" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="A57" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="B57" t="s">
+        <v>182</v>
+      </c>
+      <c r="C57" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="D57" t="s">
+        <v>182</v>
+      </c>
+      <c r="E57" s="46" t="s">
+        <v>159</v>
+      </c>
+      <c r="F57" t="s">
+        <v>182</v>
+      </c>
+      <c r="I57" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="J57" s="45" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="A58" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="B58" t="s">
+        <v>182</v>
+      </c>
+      <c r="C58" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="D58" t="s">
+        <v>182</v>
+      </c>
+      <c r="E58" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F58" t="s">
+        <v>182</v>
+      </c>
+      <c r="I58" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="J58" s="45" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="A59" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="B59" t="s">
+        <v>182</v>
+      </c>
+      <c r="C59" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="D59" t="s">
+        <v>182</v>
+      </c>
+      <c r="E59" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="F59" t="s">
+        <v>182</v>
+      </c>
+      <c r="I59" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="J59" s="45" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="A60" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B60" t="s">
+        <v>182</v>
+      </c>
+      <c r="C60" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="D60" t="s">
+        <v>182</v>
+      </c>
+      <c r="E60" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F60" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="A61" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="B61" t="s">
+        <v>182</v>
+      </c>
+      <c r="C61" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="D61" t="s">
+        <v>182</v>
+      </c>
+      <c r="E61" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="F61" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="A62" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="B62" t="s">
+        <v>182</v>
+      </c>
+      <c r="C62" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="D62" t="s">
+        <v>182</v>
+      </c>
+      <c r="E62" s="46" t="s">
+        <v>164</v>
+      </c>
+      <c r="F62" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="63" spans="1:10">
+      <c r="A63" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="B63" t="s">
+        <v>182</v>
+      </c>
+      <c r="C63" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="D63" t="s">
+        <v>182</v>
+      </c>
+      <c r="E63" s="46" t="s">
+        <v>165</v>
+      </c>
+      <c r="F63" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="64" spans="1:10">
+      <c r="A64" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="B64" t="s">
+        <v>182</v>
+      </c>
+      <c r="C64" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="D64" t="s">
+        <v>182</v>
+      </c>
+      <c r="E64" s="46" t="s">
+        <v>166</v>
+      </c>
+      <c r="F64" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="B65" t="s">
+        <v>182</v>
+      </c>
+      <c r="C65" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="D65" t="s">
+        <v>182</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>167</v>
+      </c>
+      <c r="F65" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="B66" t="s">
+        <v>182</v>
+      </c>
+      <c r="C66" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="D66" t="s">
+        <v>182</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>168</v>
+      </c>
+      <c r="F66" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="B67" t="s">
+        <v>182</v>
+      </c>
+      <c r="C67" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="D67" t="s">
+        <v>182</v>
+      </c>
+      <c r="E67" s="46" t="s">
+        <v>169</v>
+      </c>
+      <c r="F67" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="B68" t="s">
+        <v>182</v>
+      </c>
+      <c r="C68" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="D68" t="s">
+        <v>182</v>
+      </c>
+      <c r="E68" s="46" t="s">
+        <v>170</v>
+      </c>
+      <c r="F68" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="B69" t="s">
+        <v>182</v>
+      </c>
+      <c r="C69" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="D69" t="s">
+        <v>131</v>
+      </c>
+      <c r="E69" s="46" t="s">
+        <v>171</v>
+      </c>
+      <c r="F69" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="B70" t="s">
+        <v>182</v>
+      </c>
+      <c r="C70" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="D70" t="s">
+        <v>182</v>
+      </c>
+      <c r="E70" s="46" t="s">
+        <v>172</v>
+      </c>
+      <c r="F70" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="B71" t="s">
+        <v>186</v>
+      </c>
+      <c r="C71" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="D71" t="s">
+        <v>185</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>173</v>
+      </c>
+      <c r="F71" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="B72" t="s">
+        <v>138</v>
+      </c>
+      <c r="C72" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="D72" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" s="46" t="s">
+        <v>174</v>
+      </c>
+      <c r="F72" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="B73" t="s">
+        <v>137</v>
+      </c>
+      <c r="C73" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="D73" t="s">
+        <v>138</v>
+      </c>
+      <c r="E73" s="46" t="s">
+        <v>175</v>
+      </c>
+      <c r="F73" t="s">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="B74" t="s">
+        <v>185</v>
+      </c>
+      <c r="C74" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="D74" t="s">
+        <v>186</v>
+      </c>
+      <c r="E74" s="46" t="s">
+        <v>176</v>
+      </c>
+      <c r="F74" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="B75" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="C75" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="D75" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E75" s="46" t="s">
+        <v>177</v>
+      </c>
+      <c r="F75" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="G75" s="45"/>
+      <c r="H75" s="45"/>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="B76" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="C76" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="D76" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="E76" s="46" t="s">
+        <v>178</v>
+      </c>
+      <c r="F76" s="45" t="s">
+        <v>181</v>
+      </c>
+      <c r="G76" s="45"/>
+      <c r="H76" s="45"/>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="B77" t="s">
+        <v>184</v>
+      </c>
+      <c r="C77" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="D77" t="s">
+        <v>131</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>179</v>
+      </c>
+      <c r="F77" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="B78" t="s">
+        <v>131</v>
+      </c>
+      <c r="C78" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="D78" t="s">
+        <v>131</v>
+      </c>
+      <c r="E78" s="46" t="s">
+        <v>180</v>
+      </c>
+      <c r="F78" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="83" spans="5:9">
+      <c r="E83" s="50" t="s">
+        <v>294</v>
+      </c>
+      <c r="F83" s="50" t="s">
+        <v>295</v>
+      </c>
+      <c r="G83" s="50" t="s">
+        <v>296</v>
+      </c>
+      <c r="H83" s="50"/>
+      <c r="I83" s="50" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="84" spans="5:9" ht="33">
+      <c r="E84" s="51" t="s">
+        <v>298</v>
+      </c>
+      <c r="F84" s="51" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="E9"/>
-      <c r="F9"/>
-      <c r="G9" s="42"/>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="7">
+      <c r="G84" s="52" t="s">
+        <v>299</v>
+      </c>
+      <c r="H84" s="52"/>
+      <c r="I84" s="51" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="85" spans="5:9">
+      <c r="E85" s="51" t="s">
+        <v>301</v>
+      </c>
+      <c r="F85" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="32" t="s">
-        <v>6</v>
-      </c>
-      <c r="C10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>132</v>
-      </c>
-      <c r="F10" t="s">
-        <v>132</v>
-      </c>
-      <c r="G10" s="42" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="7">
+      <c r="G85" s="52" t="s">
+        <v>302</v>
+      </c>
+      <c r="H85" s="52"/>
+      <c r="I85" s="51" t="s">
+        <v>303</v>
+      </c>
+    </row>
+    <row r="86" spans="5:9" ht="33">
+      <c r="E86" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="F86" s="51" t="s">
         <v>10</v>
       </c>
-      <c r="B11" s="32" t="s">
-        <v>7</v>
-      </c>
-      <c r="C11" t="s">
-        <v>45</v>
-      </c>
-      <c r="E11" t="s">
-        <v>133</v>
-      </c>
-      <c r="F11" t="s">
-        <v>133</v>
-      </c>
-      <c r="G11" s="42" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="7">
+      <c r="G86" s="52" t="s">
+        <v>305</v>
+      </c>
+      <c r="H86" s="52"/>
+      <c r="I86" s="51" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="87" spans="5:9" ht="33">
+      <c r="E87" s="51" t="s">
+        <v>307</v>
+      </c>
+      <c r="F87" s="51" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="32" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="F12" t="s">
-        <v>134</v>
-      </c>
-      <c r="G12" s="42" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="7">
+      <c r="G87" s="52" t="s">
+        <v>308</v>
+      </c>
+      <c r="H87" s="52"/>
+      <c r="I87" s="51" t="s">
+        <v>309</v>
+      </c>
+    </row>
+    <row r="88" spans="5:9" ht="33">
+      <c r="E88" s="51" t="s">
+        <v>310</v>
+      </c>
+      <c r="F88" s="51" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="32" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="E13" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="F13" t="s">
-        <v>135</v>
-      </c>
-      <c r="G13" s="42" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="7">
+      <c r="G88" s="52" t="s">
+        <v>311</v>
+      </c>
+      <c r="H88" s="52"/>
+      <c r="I88" s="51" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="89" spans="5:9">
+      <c r="E89" s="51" t="s">
+        <v>313</v>
+      </c>
+      <c r="F89" s="51" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C14" s="42"/>
-      <c r="E14" s="42"/>
-      <c r="G14" s="42"/>
-    </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="7">
+      <c r="G89" s="52" t="s">
+        <v>314</v>
+      </c>
+      <c r="H89" s="52"/>
+      <c r="I89" s="51" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="90" spans="5:9">
+      <c r="E90" s="51" t="s">
+        <v>316</v>
+      </c>
+      <c r="F90" s="51" t="s">
         <v>14</v>
       </c>
-      <c r="B15" s="32" t="s">
-        <v>10</v>
-      </c>
-      <c r="C15" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="E15" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="F15" t="s">
-        <v>141</v>
-      </c>
-      <c r="G15" s="42" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="7">
-        <v>15</v>
-      </c>
-      <c r="B16" s="32" t="s">
-        <v>11</v>
-      </c>
-      <c r="C16" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="F16" t="s">
-        <v>140</v>
-      </c>
-      <c r="G16" s="42" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="7">
-        <v>16</v>
-      </c>
-      <c r="B17" s="32" t="s">
-        <v>12</v>
-      </c>
-      <c r="C17" s="42" t="s">
-        <v>145</v>
-      </c>
-      <c r="E17" s="42" t="s">
-        <v>98</v>
-      </c>
-      <c r="F17" t="s">
-        <v>139</v>
-      </c>
-      <c r="G17" s="42" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="7">
-        <v>17</v>
-      </c>
-      <c r="B18" s="32" t="s">
-        <v>13</v>
-      </c>
-      <c r="C18" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="E18" s="42" t="s">
-        <v>97</v>
-      </c>
-      <c r="F18" t="s">
-        <v>138</v>
-      </c>
-      <c r="G18" s="42" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="7">
-        <v>18</v>
-      </c>
-      <c r="B19" s="35" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="42"/>
-      <c r="E19" s="42"/>
-      <c r="G19" s="42"/>
-    </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="7">
-        <v>19</v>
-      </c>
-      <c r="B20" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="C20" s="42" t="s">
-        <v>101</v>
-      </c>
-      <c r="E20" s="42" t="s">
-        <v>96</v>
-      </c>
-      <c r="F20" t="s">
-        <v>137</v>
-      </c>
-      <c r="G20" s="42" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" ht="18.75" thickBot="1">
-      <c r="A21" s="8">
-        <v>20</v>
-      </c>
-      <c r="B21" s="26" t="s">
-        <v>15</v>
-      </c>
-      <c r="C21" s="42" t="s">
-        <v>102</v>
-      </c>
-      <c r="E21" s="42" t="s">
-        <v>95</v>
-      </c>
-      <c r="F21" t="s">
-        <v>136</v>
-      </c>
-      <c r="G21" s="42" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" s="5" customFormat="1" ht="18.75" thickBot="1">
-      <c r="A22" s="3"/>
-      <c r="B22" s="4"/>
-    </row>
-    <row r="23" spans="1:7">
-      <c r="A23" s="1">
-        <v>21</v>
-      </c>
-      <c r="B23" s="27" t="s">
-        <v>25</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" t="s">
-        <v>86</v>
-      </c>
-      <c r="G23" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7">
-      <c r="A24" s="1">
-        <v>22</v>
-      </c>
-      <c r="B24" s="28" t="s">
-        <v>24</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="E24" t="s">
-        <v>87</v>
-      </c>
-      <c r="F24" t="s">
-        <v>87</v>
-      </c>
-      <c r="G24" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7">
-      <c r="A25" s="1">
-        <v>23</v>
-      </c>
-      <c r="B25" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E25"/>
-      <c r="F25"/>
-    </row>
-    <row r="26" spans="1:7">
-      <c r="A26" s="1">
-        <v>24</v>
-      </c>
-      <c r="B26" s="28" t="s">
-        <v>23</v>
-      </c>
-      <c r="C26" s="42" t="s">
-        <v>103</v>
-      </c>
-      <c r="E26" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="F26" s="38" t="s">
-        <v>88</v>
-      </c>
-      <c r="G26" s="38" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7">
-      <c r="A27" s="1">
-        <v>25</v>
-      </c>
-      <c r="B27" s="28" t="s">
-        <v>22</v>
-      </c>
-      <c r="C27" s="42" t="s">
-        <v>104</v>
-      </c>
-      <c r="E27" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="F27" s="38" t="s">
-        <v>89</v>
-      </c>
-      <c r="G27" s="38" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7">
-      <c r="A28" s="1">
-        <v>26</v>
-      </c>
-      <c r="B28" s="28" t="s">
-        <v>21</v>
-      </c>
-      <c r="C28" s="42" t="s">
-        <v>105</v>
-      </c>
-      <c r="E28" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="F28" s="38" t="s">
-        <v>90</v>
-      </c>
-      <c r="G28" s="38" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7">
-      <c r="A29" s="1">
-        <v>27</v>
-      </c>
-      <c r="B29" s="28" t="s">
-        <v>20</v>
-      </c>
-      <c r="C29" s="42" t="s">
-        <v>147</v>
-      </c>
-      <c r="E29" t="s">
-        <v>84</v>
-      </c>
-      <c r="F29" t="s">
-        <v>84</v>
-      </c>
-      <c r="G29" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7">
-      <c r="A30" s="1">
-        <v>28</v>
-      </c>
-      <c r="B30" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E30"/>
-      <c r="F30"/>
-    </row>
-    <row r="31" spans="1:7">
-      <c r="A31" s="1">
-        <v>29</v>
-      </c>
-      <c r="B31" s="28" t="s">
-        <v>19</v>
-      </c>
-      <c r="C31" s="42" t="s">
-        <v>148</v>
-      </c>
-      <c r="E31" t="s">
-        <v>85</v>
-      </c>
-      <c r="F31" t="s">
-        <v>85</v>
-      </c>
-      <c r="G31" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7">
-      <c r="A32" s="1">
-        <v>30</v>
-      </c>
-      <c r="B32" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="C32" t="s">
-        <v>117</v>
-      </c>
-      <c r="E32" t="s">
-        <v>117</v>
-      </c>
-      <c r="F32" t="s">
-        <v>117</v>
-      </c>
-      <c r="G32" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="1">
-        <v>31</v>
-      </c>
-      <c r="B33" s="28" t="s">
-        <v>18</v>
-      </c>
-      <c r="C33" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="E33" t="s">
-        <v>44</v>
-      </c>
-      <c r="F33" t="s">
-        <v>44</v>
-      </c>
-      <c r="G33" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="A34" s="1">
-        <v>32</v>
-      </c>
-      <c r="B34" s="28" t="s">
-        <v>17</v>
-      </c>
-      <c r="C34" s="42" t="s">
-        <v>113</v>
-      </c>
-      <c r="E34" t="s">
-        <v>45</v>
-      </c>
-      <c r="F34" t="s">
-        <v>45</v>
-      </c>
-      <c r="G34" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1">
-        <v>33</v>
-      </c>
-      <c r="B35" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="C35" s="42" t="s">
-        <v>149</v>
-      </c>
-      <c r="E35" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F35" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G35" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="1">
-        <v>34</v>
-      </c>
-      <c r="B36" s="28" t="s">
-        <v>16</v>
-      </c>
-      <c r="C36" s="42" t="s">
-        <v>114</v>
-      </c>
-      <c r="E36" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F36" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G36" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="1">
-        <v>35</v>
-      </c>
-      <c r="B37" s="7"/>
-      <c r="C37" s="42" t="s">
-        <v>150</v>
-      </c>
-      <c r="E37" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="F37" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G37" s="43" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7">
-      <c r="A38" s="1">
-        <v>36</v>
-      </c>
-      <c r="B38" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="E38"/>
-      <c r="F38"/>
-    </row>
-    <row r="39" spans="1:7">
-      <c r="A39" s="1">
-        <v>37</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="E39"/>
-      <c r="F39"/>
-    </row>
-    <row r="40" spans="1:7">
-      <c r="A40" s="1">
-        <v>38</v>
-      </c>
-      <c r="B40" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="E40"/>
-      <c r="F40"/>
-    </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1">
-        <v>39</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" ht="18.75" thickBot="1">
-      <c r="A42" s="1">
-        <v>40</v>
-      </c>
-      <c r="B42" s="14" t="s">
-        <v>37</v>
+      <c r="G90" s="52" t="s">
+        <v>317</v>
+      </c>
+      <c r="H90" s="52"/>
+      <c r="I90" s="51" t="s">
+        <v>318</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="53" orientation="landscape" verticalDpi="0" r:id="rId1"/>
+  <mergeCells count="12">
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="I38:J38"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="E38:F38"/>
+    <mergeCell ref="C3:D3"/>
+    <mergeCell ref="E3:F3"/>
+    <mergeCell ref="I3:J3"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="A4:B4"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="C38:D38"/>
+  </mergeCells>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="landscape" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
--- a/Documentation/rp-pico-2-pin-planner-LCCboards.xlsx
+++ b/Documentation/rp-pico-2-pin-planner-LCCboards.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Attic\Documents\GitHub\LCC-Pico-Node\LCC-RPi-Pico-Board\Documentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{803B32BD-B4E6-4E85-86F6-4679D647FAB3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E203E6E8-73C8-4A6B-A839-9D45B8F40898}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11190" yWindow="1125" windowWidth="31845" windowHeight="19590" activeTab="3" xr2:uid="{9994E188-9327-AB46-AF3F-8738237FB097}"/>
   </bookViews>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1390" uniqueCount="327">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1388" uniqueCount="327">
   <si>
     <t>gp0</t>
   </si>
@@ -1421,7 +1421,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1601,8 +1601,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -6089,10 +6087,7 @@
       <c r="A30" s="42" t="s">
         <v>284</v>
       </c>
-      <c r="B30" s="65" t="s">
-        <v>231</v>
-      </c>
-      <c r="C30" t="s">
+      <c r="B30" t="s">
         <v>226</v>
       </c>
       <c r="E30" s="42" t="s">
@@ -6112,10 +6107,7 @@
       <c r="A31" s="42" t="s">
         <v>281</v>
       </c>
-      <c r="B31" s="66" t="s">
-        <v>226</v>
-      </c>
-      <c r="C31" s="45" t="s">
+      <c r="B31" s="45" t="s">
         <v>231</v>
       </c>
       <c r="E31" s="42" t="s">
